--- a/src/attributions/attributions_ig_traj_349.xlsx
+++ b/src/attributions/attributions_ig_traj_349.xlsx
@@ -1571,7 +1571,7 @@
         <v>-0</v>
       </c>
       <c r="B3" t="n">
-        <v>-0.08475896412873894</v>
+        <v>-0.1468524142653835</v>
       </c>
       <c r="C3" t="n">
         <v>-0</v>
@@ -1580,10 +1580,10 @@
         <v>-0</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.005786708595075362</v>
+        <v>0.04765319363075546</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3056299825481895</v>
+        <v>0.09737283675372109</v>
       </c>
       <c r="G3" t="n">
         <v>-0</v>
@@ -1598,7 +1598,7 @@
         <v>-0</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.005702847669996248</v>
+        <v>-0.01706824864435475</v>
       </c>
       <c r="L3" t="n">
         <v>-0</v>
@@ -1607,25 +1607,25 @@
         <v>-0</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.01359764616217597</v>
+        <v>0.02973106354875899</v>
       </c>
       <c r="O3" t="n">
-        <v>0.1246523850611411</v>
+        <v>0.03508079287834184</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>0.02462308776150503</v>
+        <v>-0.05395054519058753</v>
       </c>
       <c r="U3" t="n">
         <v>-0</v>
@@ -1634,10 +1634,10 @@
         <v>-0</v>
       </c>
       <c r="W3" t="n">
-        <v>0.1211784333901173</v>
+        <v>0.0803169603908339</v>
       </c>
       <c r="X3" t="n">
-        <v>0.09028080017642939</v>
+        <v>0.08484236581129227</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
@@ -1646,25 +1646,25 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB3" t="n">
         <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.03299928401644821</v>
+        <v>0.05228745876244088</v>
       </c>
       <c r="AD3" t="n">
         <v>-0</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.05475681950421293</v>
+        <v>-0.07475343116935732</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.03210573018330586</v>
+        <v>0.02349213979208838</v>
       </c>
       <c r="AH3" t="n">
         <v>-0</v>
@@ -1679,7 +1679,7 @@
         <v>-0</v>
       </c>
       <c r="AL3" t="n">
-        <v>-0.06094534263264872</v>
+        <v>-0.2009975967048861</v>
       </c>
       <c r="AM3" t="n">
         <v>-0</v>
@@ -1688,16 +1688,16 @@
         <v>-0</v>
       </c>
       <c r="AO3" t="n">
-        <v>-0.1211739924559416</v>
+        <v>-0.1843754060919423</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.1763120973956128</v>
+        <v>0.06690862960919058</v>
       </c>
       <c r="AQ3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS3" t="n">
         <v>-0</v>
@@ -1706,34 +1706,34 @@
         <v>-0</v>
       </c>
       <c r="AU3" t="n">
-        <v>-0.1955270916329484</v>
+        <v>-0.5431208283083041</v>
       </c>
       <c r="AV3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AW3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX3" t="n">
-        <v>0.1534140881417575</v>
+        <v>0.1023966899894944</v>
       </c>
       <c r="AY3" t="n">
-        <v>0.5308168378096633</v>
+        <v>0.1489205162698689</v>
       </c>
       <c r="AZ3" t="n">
         <v>-0</v>
       </c>
       <c r="BA3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BB3" t="n">
         <v>-0</v>
       </c>
       <c r="BC3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD3" t="n">
-        <v>-0.06451902496142455</v>
+        <v>0.05876132877934464</v>
       </c>
       <c r="BE3" t="n">
         <v>-0</v>
@@ -1742,52 +1742,52 @@
         <v>-0</v>
       </c>
       <c r="BG3" t="n">
-        <v>0.005964188018632944</v>
+        <v>0.03664963523803285</v>
       </c>
       <c r="BH3" t="n">
-        <v>0.0843456444409221</v>
+        <v>0.01090772047250809</v>
       </c>
       <c r="BI3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BK3" t="n">
         <v>0</v>
       </c>
       <c r="BL3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BM3" t="n">
-        <v>-0.07031675944608752</v>
+        <v>0.01780492880477463</v>
       </c>
       <c r="BN3" t="n">
         <v>0</v>
       </c>
       <c r="BO3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BP3" t="n">
-        <v>0.01383556416098677</v>
+        <v>-0.06887358989448854</v>
       </c>
       <c r="BQ3" t="n">
-        <v>0.054836412002302</v>
+        <v>-0.0700795537235795</v>
       </c>
       <c r="BR3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BS3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BT3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BU3" t="n">
         <v>-0</v>
       </c>
       <c r="BV3" t="n">
-        <v>-0.07822408625823436</v>
+        <v>-0.3742651075943039</v>
       </c>
       <c r="BW3" t="n">
         <v>-0</v>
@@ -1796,43 +1796,43 @@
         <v>-0</v>
       </c>
       <c r="BY3" t="n">
-        <v>0.1098523003257043</v>
+        <v>0.07018370515341119</v>
       </c>
       <c r="BZ3" t="n">
-        <v>0.2637926986621896</v>
+        <v>0.1734676719529208</v>
       </c>
       <c r="CA3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CB3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CC3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CD3" t="n">
         <v>0</v>
       </c>
       <c r="CE3" t="n">
-        <v>0.04422868175637174</v>
+        <v>0.2426479567537415</v>
       </c>
       <c r="CF3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CG3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CH3" t="n">
-        <v>0.02318474715995898</v>
+        <v>-0.01662848978937133</v>
       </c>
       <c r="CI3" t="n">
-        <v>-0.1380091629056259</v>
+        <v>-0.1159975532074347</v>
       </c>
       <c r="CJ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL3" t="n">
         <v>0</v>
@@ -1841,7 +1841,7 @@
         <v>-0</v>
       </c>
       <c r="CN3" t="n">
-        <v>0.001888471666406638</v>
+        <v>0.1341560888295332</v>
       </c>
       <c r="CO3" t="n">
         <v>0</v>
@@ -1850,43 +1850,43 @@
         <v>0</v>
       </c>
       <c r="CQ3" t="n">
-        <v>-0.1111842321490525</v>
+        <v>-0.02325448042469054</v>
       </c>
       <c r="CR3" t="n">
-        <v>0.009710467549192027</v>
+        <v>-0.05589766363982875</v>
       </c>
       <c r="CS3" t="n">
         <v>0</v>
       </c>
       <c r="CT3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CU3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CV3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW3" t="n">
-        <v>0.03826937747275013</v>
+        <v>0.2440277935157821</v>
       </c>
       <c r="CX3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CY3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CZ3" t="n">
-        <v>0.01089412541906064</v>
+        <v>-0.01911186238432347</v>
       </c>
       <c r="DA3" t="n">
-        <v>-0.163014022904211</v>
+        <v>-0.1187077503027596</v>
       </c>
       <c r="DB3" t="n">
         <v>0</v>
       </c>
       <c r="DC3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD3" t="n">
         <v>-0</v>
@@ -1895,61 +1895,61 @@
         <v>-0</v>
       </c>
       <c r="DF3" t="n">
-        <v>-0.04696352699095778</v>
+        <v>0.001521999022370369</v>
       </c>
       <c r="DG3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DI3" t="n">
-        <v>-0.04675257002786942</v>
+        <v>0.03064505056540578</v>
       </c>
       <c r="DJ3" t="n">
-        <v>0.0153563755275643</v>
+        <v>-0.03966448199039028</v>
       </c>
       <c r="DK3" t="n">
         <v>-0</v>
       </c>
       <c r="DL3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DO3" t="n">
-        <v>-0.02596693297279041</v>
+        <v>0.1448890460232877</v>
       </c>
       <c r="DP3" t="n">
         <v>0</v>
       </c>
       <c r="DQ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DR3" t="n">
-        <v>-0.03667548048977033</v>
+        <v>-0.03490491482424421</v>
       </c>
       <c r="DS3" t="n">
-        <v>-0.02294208716261286</v>
+        <v>-0.03370493626781867</v>
       </c>
       <c r="DT3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DU3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW3" t="n">
         <v>0</v>
       </c>
       <c r="DX3" t="n">
-        <v>-0.0001475189772914169</v>
+        <v>-0.1250759446422738</v>
       </c>
       <c r="DY3" t="n">
         <v>-0</v>
@@ -1958,10 +1958,10 @@
         <v>-0</v>
       </c>
       <c r="EA3" t="n">
-        <v>0.07313937609631559</v>
+        <v>0.0216304405968441</v>
       </c>
       <c r="EB3" t="n">
-        <v>0.01872208339763147</v>
+        <v>0.2989832086204988</v>
       </c>
       <c r="EC3" t="n">
         <v>0</v>
@@ -1970,40 +1970,40 @@
         <v>-0</v>
       </c>
       <c r="EE3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EF3" t="n">
         <v>0</v>
       </c>
       <c r="EG3" t="n">
-        <v>0.05421927578070387</v>
+        <v>0.1437283454315371</v>
       </c>
       <c r="EH3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI3" t="n">
         <v>-0</v>
       </c>
       <c r="EJ3" t="n">
-        <v>-0.02693101276389425</v>
+        <v>0.004751108763261551</v>
       </c>
       <c r="EK3" t="n">
-        <v>-0.1226727652879778</v>
+        <v>-0.05424944123172233</v>
       </c>
       <c r="EL3" t="n">
         <v>0</v>
       </c>
       <c r="EM3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO3" t="n">
         <v>-0</v>
       </c>
       <c r="EP3" t="n">
-        <v>0.04271237113745027</v>
+        <v>0.1318779013849795</v>
       </c>
       <c r="EQ3" t="n">
         <v>0</v>
@@ -2012,10 +2012,10 @@
         <v>0</v>
       </c>
       <c r="ES3" t="n">
-        <v>0.02446560008477118</v>
+        <v>-0.04817906523624018</v>
       </c>
       <c r="ET3" t="n">
-        <v>-0.04796009246986633</v>
+        <v>-0.009017819969299382</v>
       </c>
       <c r="EU3" t="n">
         <v>-0</v>
@@ -2024,31 +2024,31 @@
         <v>-0</v>
       </c>
       <c r="EW3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY3" t="n">
-        <v>0.03091848564588136</v>
+        <v>0.2650023256820411</v>
       </c>
       <c r="EZ3" t="n">
         <v>0</v>
       </c>
       <c r="FA3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FB3" t="n">
-        <v>-0.00811061420687415</v>
+        <v>-0.01318617854922261</v>
       </c>
       <c r="FC3" t="n">
-        <v>-0.1264849610737154</v>
+        <v>-0.1152500568988927</v>
       </c>
       <c r="FD3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FE3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF3" t="n">
         <v>0</v>
@@ -2057,73 +2057,73 @@
         <v>-0</v>
       </c>
       <c r="FH3" t="n">
-        <v>0.057067222950919</v>
+        <v>0.1031404140764325</v>
       </c>
       <c r="FI3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ3" t="n">
         <v>0</v>
       </c>
       <c r="FK3" t="n">
-        <v>0.07168348562353966</v>
+        <v>0.1126402811641876</v>
       </c>
       <c r="FL3" t="n">
-        <v>-0.1418417552274748</v>
+        <v>0.02690842878710476</v>
       </c>
       <c r="FM3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN3" t="n">
         <v>-0</v>
       </c>
       <c r="FO3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FP3" t="n">
         <v>0</v>
       </c>
       <c r="FQ3" t="n">
-        <v>0.09703648883869445</v>
+        <v>0.2543705629088246</v>
       </c>
       <c r="FR3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS3" t="n">
         <v>0</v>
       </c>
       <c r="FT3" t="n">
-        <v>-0.009888074286467484</v>
+        <v>-0.005097189052391137</v>
       </c>
       <c r="FU3" t="n">
-        <v>-0.2059139391088503</v>
+        <v>-0.135538354466206</v>
       </c>
       <c r="FV3" t="n">
         <v>0</v>
       </c>
       <c r="FW3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY3" t="n">
         <v>0</v>
       </c>
       <c r="FZ3" t="n">
-        <v>-0.001985008452791411</v>
+        <v>0.09609038089671929</v>
       </c>
       <c r="GA3" t="n">
         <v>0</v>
       </c>
       <c r="GB3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GC3" t="n">
         <v>-0</v>
       </c>
       <c r="GD3" t="n">
-        <v>0.03151431752747932</v>
+        <v>-0.01665429880132434</v>
       </c>
       <c r="GE3" t="n">
         <v>0</v>
@@ -2143,25 +2143,25 @@
         <v>-0</v>
       </c>
       <c r="C4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.05329596814568315</v>
+        <v>-0.007276082139414651</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1711106691467864</v>
+        <v>0.03747947258168277</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.05968372731074184</v>
+        <v>-0.005333286086061487</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -2173,55 +2173,55 @@
         <v>-0</v>
       </c>
       <c r="M4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.02688100032604157</v>
+        <v>0.006518963609217137</v>
       </c>
       <c r="O4" t="n">
-        <v>0.07676770137512981</v>
+        <v>0.04311579320853284</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.006669440448529174</v>
+        <v>0.0008431879612787985</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T4" t="n">
         <v>-0</v>
       </c>
       <c r="U4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="W4" t="n">
-        <v>0.06867141410343106</v>
+        <v>0.01271291533596496</v>
       </c>
       <c r="X4" t="n">
-        <v>0.09908972744778273</v>
+        <v>0.03673519239624753</v>
       </c>
       <c r="Y4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>-0.09930910554600134</v>
+        <v>0.03523571686537452</v>
       </c>
       <c r="AA4" t="n">
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AD4" t="n">
         <v>-0</v>
@@ -2230,22 +2230,22 @@
         <v>-0</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.05205130401462965</v>
+        <v>-0.02009906558253118</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.02185539106083013</v>
+        <v>0.02963774643001061</v>
       </c>
       <c r="AH4" t="n">
         <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>-0.00905801424389387</v>
+        <v>0.008229533224848375</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL4" t="n">
         <v>-0</v>
@@ -2254,19 +2254,19 @@
         <v>0</v>
       </c>
       <c r="AN4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO4" t="n">
-        <v>-0.0612549390406004</v>
+        <v>-0.02537384744617591</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.05740983719993595</v>
+        <v>-0.02376150209888506</v>
       </c>
       <c r="AQ4" t="n">
         <v>-0</v>
       </c>
       <c r="AR4" t="n">
-        <v>-0.05154750991247693</v>
+        <v>0.002678538454497914</v>
       </c>
       <c r="AS4" t="n">
         <v>-0</v>
@@ -2284,43 +2284,43 @@
         <v>-0</v>
       </c>
       <c r="AX4" t="n">
-        <v>0.1286080346298448</v>
+        <v>0.03758750527715826</v>
       </c>
       <c r="AY4" t="n">
-        <v>0.2754753627520651</v>
+        <v>0.1491580931719007</v>
       </c>
       <c r="AZ4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA4" t="n">
-        <v>-0.05957860410381412</v>
+        <v>0.0004210045849520095</v>
       </c>
       <c r="BB4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC4" t="n">
         <v>0</v>
       </c>
       <c r="BD4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BE4" t="n">
         <v>-0</v>
       </c>
       <c r="BF4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BG4" t="n">
-        <v>-0.08864623111609801</v>
+        <v>-0.04642001227362048</v>
       </c>
       <c r="BH4" t="n">
-        <v>0.002285435968076502</v>
+        <v>-0.03580837581094663</v>
       </c>
       <c r="BI4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ4" t="n">
-        <v>-0.03065429173625001</v>
+        <v>-0.01783085538541615</v>
       </c>
       <c r="BK4" t="n">
         <v>0</v>
@@ -2335,55 +2335,55 @@
         <v>-0</v>
       </c>
       <c r="BO4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BP4" t="n">
-        <v>-0.09143114316651604</v>
+        <v>0.01172778850812759</v>
       </c>
       <c r="BQ4" t="n">
-        <v>0.0417771892739174</v>
+        <v>0.01268879940029882</v>
       </c>
       <c r="BR4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BS4" t="n">
-        <v>0.05976393616533023</v>
+        <v>0.01522758869472888</v>
       </c>
       <c r="BT4" t="n">
         <v>-0</v>
       </c>
       <c r="BU4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV4" t="n">
         <v>-0</v>
       </c>
       <c r="BW4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BY4" t="n">
-        <v>0.09579388170981258</v>
+        <v>0.006302486229596396</v>
       </c>
       <c r="BZ4" t="n">
-        <v>0.2354398029360496</v>
+        <v>0.05653503780189552</v>
       </c>
       <c r="CA4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CB4" t="n">
-        <v>-0.06019720350742794</v>
+        <v>-0.005745870952998884</v>
       </c>
       <c r="CC4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CD4" t="n">
         <v>-0</v>
       </c>
       <c r="CE4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CF4" t="n">
         <v>-0</v>
@@ -2392,16 +2392,16 @@
         <v>-0</v>
       </c>
       <c r="CH4" t="n">
-        <v>0.04232194088532488</v>
+        <v>0.00440298574171669</v>
       </c>
       <c r="CI4" t="n">
-        <v>-0.07912895292230784</v>
+        <v>-0.02077549001414934</v>
       </c>
       <c r="CJ4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK4" t="n">
-        <v>0.05820966915748643</v>
+        <v>0.02105583681902378</v>
       </c>
       <c r="CL4" t="n">
         <v>0</v>
@@ -2410,7 +2410,7 @@
         <v>-0</v>
       </c>
       <c r="CN4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CO4" t="n">
         <v>0</v>
@@ -2419,79 +2419,79 @@
         <v>0</v>
       </c>
       <c r="CQ4" t="n">
-        <v>-0.05084772779648029</v>
+        <v>-0.01213843509164773</v>
       </c>
       <c r="CR4" t="n">
-        <v>0.01852773686308323</v>
+        <v>0.02232965564209932</v>
       </c>
       <c r="CS4" t="n">
         <v>-0</v>
       </c>
       <c r="CT4" t="n">
-        <v>0.02348896290039004</v>
+        <v>0.03065693760003023</v>
       </c>
       <c r="CU4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW4" t="n">
         <v>0</v>
       </c>
       <c r="CX4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY4" t="n">
         <v>0</v>
       </c>
       <c r="CZ4" t="n">
-        <v>0.01812361736128678</v>
+        <v>0.002685249141503774</v>
       </c>
       <c r="DA4" t="n">
-        <v>-0.07158947200852442</v>
+        <v>-0.03095427568476869</v>
       </c>
       <c r="DB4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC4" t="n">
-        <v>0.08089516411941092</v>
+        <v>0.01060465597269717</v>
       </c>
       <c r="DD4" t="n">
         <v>-0</v>
       </c>
       <c r="DE4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DF4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DG4" t="n">
         <v>0</v>
       </c>
       <c r="DH4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.05022105401384689</v>
+        <v>-0.006345507938115363</v>
       </c>
       <c r="DJ4" t="n">
-        <v>-0.0294795461129237</v>
+        <v>-0.00165704900731162</v>
       </c>
       <c r="DK4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.02095391991995531</v>
+        <v>0.005340588553685395</v>
       </c>
       <c r="DM4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN4" t="n">
         <v>-0</v>
       </c>
       <c r="DO4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DP4" t="n">
         <v>-0</v>
@@ -2500,43 +2500,43 @@
         <v>-0</v>
       </c>
       <c r="DR4" t="n">
-        <v>0.01142165161516213</v>
+        <v>0.06072850418359734</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.00315751028996109</v>
+        <v>-0.05738897400960964</v>
       </c>
       <c r="DT4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DU4" t="n">
-        <v>-0.02791790953511505</v>
+        <v>0.005040064616239775</v>
       </c>
       <c r="DV4" t="n">
         <v>0</v>
       </c>
       <c r="DW4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DY4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DZ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA4" t="n">
-        <v>-0.05553170382863402</v>
+        <v>0.02976963217390027</v>
       </c>
       <c r="EB4" t="n">
-        <v>0.007935860381186667</v>
+        <v>-0.03327452937628671</v>
       </c>
       <c r="EC4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ED4" t="n">
-        <v>0.005162156856288169</v>
+        <v>-0.01985924140950908</v>
       </c>
       <c r="EE4" t="n">
         <v>0</v>
@@ -2548,76 +2548,76 @@
         <v>-0</v>
       </c>
       <c r="EH4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI4" t="n">
         <v>-0</v>
       </c>
       <c r="EJ4" t="n">
-        <v>-0.003839416167527307</v>
+        <v>-0.01607561528932106</v>
       </c>
       <c r="EK4" t="n">
-        <v>-0.05235065471539233</v>
+        <v>-0.008792676386446865</v>
       </c>
       <c r="EL4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM4" t="n">
-        <v>0.04035017195251119</v>
+        <v>0.01165749434435444</v>
       </c>
       <c r="EN4" t="n">
         <v>0</v>
       </c>
       <c r="EO4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP4" t="n">
         <v>-0</v>
       </c>
       <c r="EQ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ES4" t="n">
-        <v>0.04393366506871242</v>
+        <v>-0.01454795794988933</v>
       </c>
       <c r="ET4" t="n">
-        <v>0.005798923258098328</v>
+        <v>-0.03848522505193371</v>
       </c>
       <c r="EU4" t="n">
         <v>-0</v>
       </c>
       <c r="EV4" t="n">
-        <v>0.1075094874173566</v>
+        <v>-0.005364519975092611</v>
       </c>
       <c r="EW4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY4" t="n">
         <v>-0</v>
       </c>
       <c r="EZ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA4" t="n">
         <v>-0</v>
       </c>
       <c r="FB4" t="n">
-        <v>0.03101234279652077</v>
+        <v>-0.01238831352736359</v>
       </c>
       <c r="FC4" t="n">
-        <v>-0.06984453299286347</v>
+        <v>-0.02765470818227359</v>
       </c>
       <c r="FD4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE4" t="n">
-        <v>0.083103509614033</v>
+        <v>0.01872921437744366</v>
       </c>
       <c r="FF4" t="n">
         <v>0</v>
@@ -2626,58 +2626,58 @@
         <v>-0</v>
       </c>
       <c r="FH4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FI4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FJ4" t="n">
         <v>0</v>
       </c>
       <c r="FK4" t="n">
-        <v>-0.04923040422187826</v>
+        <v>-0.01306177056249307</v>
       </c>
       <c r="FL4" t="n">
-        <v>-0.1191438760183637</v>
+        <v>0.01764985124902873</v>
       </c>
       <c r="FM4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN4" t="n">
-        <v>0.08010835603687844</v>
+        <v>0.01897897484836169</v>
       </c>
       <c r="FO4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP4" t="n">
         <v>-0</v>
       </c>
       <c r="FQ4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FR4" t="n">
         <v>-0</v>
       </c>
       <c r="FS4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FT4" t="n">
-        <v>-0.09611703669102474</v>
+        <v>-0.07591550934368896</v>
       </c>
       <c r="FU4" t="n">
-        <v>0.08677441763649087</v>
+        <v>-0.1215595979358823</v>
       </c>
       <c r="FV4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW4" t="n">
-        <v>1.165290966977967e-05</v>
+        <v>0.007323174574305368</v>
       </c>
       <c r="FX4" t="n">
         <v>-0</v>
       </c>
       <c r="FY4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ4" t="n">
         <v>-0</v>
@@ -2686,19 +2686,19 @@
         <v>-0</v>
       </c>
       <c r="GB4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GC4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD4" t="n">
-        <v>0.003616198959147295</v>
+        <v>-0.02910868532306088</v>
       </c>
       <c r="GE4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF4" t="n">
-        <v>-0.04966778113643917</v>
+        <v>-0.01641965167283736</v>
       </c>
       <c r="GG4" t="n">
         <v>0</v>
@@ -2712,13 +2712,13 @@
         <v>-0</v>
       </c>
       <c r="C5" t="n">
-        <v>-5.8373673341386e-11</v>
+        <v>-5.171873826158464e-11</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1235219561018443</v>
+        <v>0.08226308342123288</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.0288918517326234</v>
+        <v>0.07058185502899199</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -2727,31 +2727,31 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.006432349182565227</v>
+        <v>-0.005172592256198785</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1190470626424984</v>
+        <v>0.05521709020255243</v>
       </c>
       <c r="N5" t="n">
-        <v>0.02969783707799712</v>
+        <v>0.07419697969673872</v>
       </c>
       <c r="O5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -2760,31 +2760,31 @@
         <v>-0</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.05378042251152168</v>
+        <v>-0.04404111237328943</v>
       </c>
       <c r="V5" t="n">
-        <v>0.07739313081290328</v>
+        <v>0.03215131110430586</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.0145018666272192</v>
+        <v>-0.03642288217603749</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z5" t="n">
         <v>-0</v>
       </c>
       <c r="AA5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
         <v>0</v>
@@ -2793,67 +2793,67 @@
         <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>2.073084074340912e-11</v>
+        <v>3.785772100425648e-11</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.04017615726853676</v>
+        <v>-0.06661494228298689</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.001055943520072611</v>
+        <v>0.03335499406623372</v>
       </c>
       <c r="AG5" t="n">
         <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ5" t="n">
         <v>-0</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.005640001977420554</v>
+        <v>-0.06370772204469929</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.05855191457481828</v>
+        <v>0.08240672550025688</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.02511628336766595</v>
+        <v>-0.005887371481762033</v>
       </c>
       <c r="AP5" t="n">
         <v>0</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS5" t="n">
         <v>0</v>
       </c>
       <c r="AT5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU5" t="n">
         <v>0</v>
       </c>
       <c r="AV5" t="n">
-        <v>-0.1160166839997872</v>
+        <v>-0.1808004810108951</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.1212709722842446</v>
+        <v>0.18464195437902</v>
       </c>
       <c r="AX5" t="n">
-        <v>-0.1798194155884322</v>
+        <v>-0.04998125974629213</v>
       </c>
       <c r="AY5" t="n">
         <v>0</v>
@@ -2874,13 +2874,13 @@
         <v>-0</v>
       </c>
       <c r="BE5" t="n">
-        <v>-0.04115282254035441</v>
+        <v>0.004878603844071338</v>
       </c>
       <c r="BF5" t="n">
-        <v>0.04643219650533725</v>
+        <v>-0.07165763003506262</v>
       </c>
       <c r="BG5" t="n">
-        <v>0.02052463504623743</v>
+        <v>-0.1114978510340356</v>
       </c>
       <c r="BH5" t="n">
         <v>-0</v>
@@ -2889,7 +2889,7 @@
         <v>0</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK5" t="n">
         <v>-0</v>
@@ -2898,16 +2898,16 @@
         <v>0</v>
       </c>
       <c r="BM5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BN5" t="n">
-        <v>0.03635329161396462</v>
+        <v>0.04790465989432859</v>
       </c>
       <c r="BO5" t="n">
-        <v>-0.04375682789066451</v>
+        <v>0.09949945901330558</v>
       </c>
       <c r="BP5" t="n">
-        <v>-0.07728520312478701</v>
+        <v>0.1147896680995294</v>
       </c>
       <c r="BQ5" t="n">
         <v>0</v>
@@ -2916,85 +2916,85 @@
         <v>-0</v>
       </c>
       <c r="BS5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT5" t="n">
         <v>0</v>
       </c>
       <c r="BU5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BW5" t="n">
-        <v>-0.1102079956938756</v>
+        <v>-0.1054881567241051</v>
       </c>
       <c r="BX5" t="n">
-        <v>0.1358113981544033</v>
+        <v>0.1050706478880057</v>
       </c>
       <c r="BY5" t="n">
-        <v>-0.1122761685369115</v>
+        <v>0.009078143612639101</v>
       </c>
       <c r="BZ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CA5" t="n">
         <v>-0</v>
       </c>
       <c r="CB5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CD5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CE5" t="n">
         <v>0</v>
       </c>
       <c r="CF5" t="n">
-        <v>0.04631962902649762</v>
+        <v>0.07481439320172593</v>
       </c>
       <c r="CG5" t="n">
-        <v>-0.06701920578215495</v>
+        <v>0.003711131153940596</v>
       </c>
       <c r="CH5" t="n">
-        <v>0.002487429695050146</v>
+        <v>-0.0854770189046071</v>
       </c>
       <c r="CI5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CL5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CN5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CO5" t="n">
-        <v>0.01437968528448127</v>
+        <v>0.005779779004463955</v>
       </c>
       <c r="CP5" t="n">
-        <v>-0.006029926737581152</v>
+        <v>0.06956198939145032</v>
       </c>
       <c r="CQ5" t="n">
-        <v>0.03853138675569742</v>
+        <v>0.0910494158229017</v>
       </c>
       <c r="CR5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT5" t="n">
         <v>0</v>
@@ -3006,43 +3006,43 @@
         <v>-0</v>
       </c>
       <c r="CW5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CX5" t="n">
-        <v>0.02695538874796563</v>
+        <v>0.06968896292656884</v>
       </c>
       <c r="CY5" t="n">
-        <v>-0.06323037374538891</v>
+        <v>-0.007700232329191999</v>
       </c>
       <c r="CZ5" t="n">
-        <v>0.01047063575262586</v>
+        <v>-0.07092836509345803</v>
       </c>
       <c r="DA5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DB5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DD5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE5" t="n">
         <v>0</v>
       </c>
       <c r="DF5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DG5" t="n">
-        <v>0.01021894140229481</v>
+        <v>0.03503705394657008</v>
       </c>
       <c r="DH5" t="n">
-        <v>-0.04946571932143475</v>
+        <v>-0.05558867729234562</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.004853306244189109</v>
+        <v>-0.02004108261818394</v>
       </c>
       <c r="DJ5" t="n">
         <v>0</v>
@@ -3051,25 +3051,25 @@
         <v>0</v>
       </c>
       <c r="DL5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DM5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DO5" t="n">
         <v>0</v>
       </c>
       <c r="DP5" t="n">
-        <v>0.01193365782982534</v>
+        <v>-0.0004101844379681922</v>
       </c>
       <c r="DQ5" t="n">
-        <v>-0.02559592789375077</v>
+        <v>-0.01597012387156517</v>
       </c>
       <c r="DR5" t="n">
-        <v>0.03832338995281433</v>
+        <v>0.01515282447232605</v>
       </c>
       <c r="DS5" t="n">
         <v>-0</v>
@@ -3078,25 +3078,25 @@
         <v>-0</v>
       </c>
       <c r="DU5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DV5" t="n">
         <v>-0</v>
       </c>
       <c r="DW5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DX5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DY5" t="n">
-        <v>0.02444244805272475</v>
+        <v>-0.08664327171411827</v>
       </c>
       <c r="DZ5" t="n">
-        <v>0.03949050971208064</v>
+        <v>-0.09122576082289049</v>
       </c>
       <c r="EA5" t="n">
-        <v>0.04698269686633406</v>
+        <v>0.002728924986871808</v>
       </c>
       <c r="EB5" t="n">
         <v>-0</v>
@@ -3105,106 +3105,106 @@
         <v>0</v>
       </c>
       <c r="ED5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EE5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF5" t="n">
         <v>0</v>
       </c>
       <c r="EG5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EH5" t="n">
-        <v>0.05700244725237039</v>
+        <v>0.03745697224636105</v>
       </c>
       <c r="EI5" t="n">
-        <v>-0.07624139975365592</v>
+        <v>-0.002354121849112942</v>
       </c>
       <c r="EJ5" t="n">
-        <v>0.02173730222302824</v>
+        <v>-0.1121504405779203</v>
       </c>
       <c r="EK5" t="n">
         <v>0</v>
       </c>
       <c r="EL5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EM5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EP5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EQ5" t="n">
-        <v>0.05366081006835148</v>
+        <v>-0.02228633249649049</v>
       </c>
       <c r="ER5" t="n">
-        <v>-0.03904984431554241</v>
+        <v>-0.06740179683621941</v>
       </c>
       <c r="ES5" t="n">
-        <v>-0.0236817794721782</v>
+        <v>-0.04777153456593867</v>
       </c>
       <c r="ET5" t="n">
         <v>-0</v>
       </c>
       <c r="EU5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV5" t="n">
         <v>-0</v>
       </c>
       <c r="EW5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EY5" t="n">
         <v>0</v>
       </c>
       <c r="EZ5" t="n">
-        <v>0.0312854921682145</v>
+        <v>0.07069314768533209</v>
       </c>
       <c r="FA5" t="n">
-        <v>-0.06311809081641902</v>
+        <v>-0.006937066997913556</v>
       </c>
       <c r="FB5" t="n">
-        <v>0.000651650140042561</v>
+        <v>-0.08774432294118957</v>
       </c>
       <c r="FC5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FD5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FE5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FF5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG5" t="n">
         <v>0</v>
       </c>
       <c r="FH5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FI5" t="n">
-        <v>0.03471523494738323</v>
+        <v>0.08986968564999549</v>
       </c>
       <c r="FJ5" t="n">
-        <v>0.02737503072985418</v>
+        <v>-0.002501273868903064</v>
       </c>
       <c r="FK5" t="n">
-        <v>-0.02169671985007909</v>
+        <v>-0.1016777830359367</v>
       </c>
       <c r="FL5" t="n">
         <v>0</v>
@@ -3213,52 +3213,52 @@
         <v>-0</v>
       </c>
       <c r="FN5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FP5" t="n">
         <v>0</v>
       </c>
       <c r="FQ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FR5" t="n">
-        <v>0.01096864268908549</v>
+        <v>0.00366844842265765</v>
       </c>
       <c r="FS5" t="n">
-        <v>0.005409502938653475</v>
+        <v>-0.007792637740198561</v>
       </c>
       <c r="FT5" t="n">
-        <v>-0.002200636814853804</v>
+        <v>0.06301818931583028</v>
       </c>
       <c r="FU5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FV5" t="n">
         <v>0</v>
       </c>
       <c r="FW5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX5" t="n">
         <v>-0</v>
       </c>
       <c r="FY5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FZ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GA5" t="n">
-        <v>0.02256164151164745</v>
+        <v>0.08602947515996279</v>
       </c>
       <c r="GB5" t="n">
-        <v>0.009197817359931762</v>
+        <v>-0.09966593000376901</v>
       </c>
       <c r="GC5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD5" t="n">
         <v>0</v>
@@ -3267,7 +3267,7 @@
         <v>0</v>
       </c>
       <c r="GF5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG5" t="n">
         <v>0</v>
@@ -3847,19 +3847,19 @@
         <v>0</v>
       </c>
       <c r="B7" t="n">
-        <v>0.0865216154194231</v>
+        <v>0.1220980397368658</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.06692003231614591</v>
+        <v>-0.02325839531300927</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.02875629290221898</v>
+        <v>-0.03902896004287925</v>
       </c>
       <c r="G7" t="n">
         <v>-0</v>
@@ -3871,91 +3871,91 @@
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0432549533352687</v>
+        <v>0.1235980108286532</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.04723013596592543</v>
+        <v>-0.04949580437066389</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.02069043240531885</v>
+        <v>-0.02355061260048539</v>
       </c>
       <c r="P7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T7" t="n">
-        <v>0.01804752275353059</v>
+        <v>0.08527701677951824</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.008615945888080182</v>
+        <v>-0.02837107336813436</v>
       </c>
       <c r="X7" t="n">
-        <v>0.02498067717105192</v>
+        <v>0.04494093881598217</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB7" t="n">
         <v>-0</v>
       </c>
       <c r="AC7" t="n">
-        <v>-0.008986587921596465</v>
+        <v>0.01044723948821521</v>
       </c>
       <c r="AD7" t="n">
         <v>-0</v>
       </c>
       <c r="AE7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>-0.007672090963944738</v>
+        <v>0.02105752623070321</v>
       </c>
       <c r="AG7" t="n">
-        <v>-0.008002822311013683</v>
+        <v>-0.04332049211646304</v>
       </c>
       <c r="AH7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
         <v>-0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.04276722926176894</v>
+        <v>0.02964857820179862</v>
       </c>
       <c r="AM7" t="n">
         <v>0</v>
@@ -3964,52 +3964,52 @@
         <v>0</v>
       </c>
       <c r="AO7" t="n">
-        <v>-0.007397985650772066</v>
+        <v>-0.03010472998004583</v>
       </c>
       <c r="AP7" t="n">
-        <v>-0.002497985774769037</v>
+        <v>-0.04700770502868733</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR7" t="n">
         <v>-0</v>
       </c>
       <c r="AS7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT7" t="n">
         <v>-0</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.1269428971938504</v>
+        <v>0.3163513687909205</v>
       </c>
       <c r="AV7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW7" t="n">
         <v>0</v>
       </c>
       <c r="AX7" t="n">
-        <v>-0.06326384189353827</v>
+        <v>-0.1499296469661328</v>
       </c>
       <c r="AY7" t="n">
-        <v>-0.04422284239234422</v>
+        <v>-0.1462996944759825</v>
       </c>
       <c r="AZ7" t="n">
         <v>0</v>
       </c>
       <c r="BA7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BB7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD7" t="n">
-        <v>0.02976949100100432</v>
+        <v>-0.06172349362819905</v>
       </c>
       <c r="BE7" t="n">
         <v>0</v>
@@ -4018,70 +4018,70 @@
         <v>0</v>
       </c>
       <c r="BG7" t="n">
-        <v>-0.05724960542710013</v>
+        <v>-0.02319965698980324</v>
       </c>
       <c r="BH7" t="n">
-        <v>-0.008593557159747217</v>
+        <v>0.007028687843660774</v>
       </c>
       <c r="BI7" t="n">
         <v>-0</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BL7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.04449864124390693</v>
+        <v>0.09858529462615503</v>
       </c>
       <c r="BN7" t="n">
         <v>-0</v>
       </c>
       <c r="BO7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BP7" t="n">
-        <v>0.01061836464040484</v>
+        <v>0.1055286629937307</v>
       </c>
       <c r="BQ7" t="n">
-        <v>0.01686856008834947</v>
+        <v>0.08791263343988555</v>
       </c>
       <c r="BR7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU7" t="n">
         <v>-0</v>
       </c>
       <c r="BV7" t="n">
-        <v>0.05837189962540962</v>
+        <v>0.2074878223653781</v>
       </c>
       <c r="BW7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX7" t="n">
         <v>0</v>
       </c>
       <c r="BY7" t="n">
-        <v>-0.02809205269851037</v>
+        <v>-0.05954451682306171</v>
       </c>
       <c r="BZ7" t="n">
-        <v>-0.005058889396433117</v>
+        <v>-0.01438222950637652</v>
       </c>
       <c r="CA7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC7" t="n">
         <v>-0</v>
@@ -4090,25 +4090,25 @@
         <v>-0</v>
       </c>
       <c r="CE7" t="n">
-        <v>-0.02016523205699673</v>
+        <v>-0.05494647109504519</v>
       </c>
       <c r="CF7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG7" t="n">
         <v>0</v>
       </c>
       <c r="CH7" t="n">
-        <v>0.01768927966900448</v>
+        <v>0.02828108189612986</v>
       </c>
       <c r="CI7" t="n">
-        <v>0.0160868632076541</v>
+        <v>0.02471685850628428</v>
       </c>
       <c r="CJ7" t="n">
         <v>-0</v>
       </c>
       <c r="CK7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CL7" t="n">
         <v>-0</v>
@@ -4117,19 +4117,19 @@
         <v>0</v>
       </c>
       <c r="CN7" t="n">
-        <v>0.008464848612403649</v>
+        <v>-0.04269150068073082</v>
       </c>
       <c r="CO7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CQ7" t="n">
-        <v>-0.003444944250281142</v>
+        <v>0.04663773721143955</v>
       </c>
       <c r="CR7" t="n">
-        <v>-0.005144964457170661</v>
+        <v>-0.003113135562728391</v>
       </c>
       <c r="CS7" t="n">
         <v>-0</v>
@@ -4138,31 +4138,31 @@
         <v>-0</v>
       </c>
       <c r="CU7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CV7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW7" t="n">
-        <v>-0.008500724997003706</v>
+        <v>-0.05313978583359964</v>
       </c>
       <c r="CX7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY7" t="n">
         <v>-0</v>
       </c>
       <c r="CZ7" t="n">
-        <v>0.01431440322001988</v>
+        <v>0.01624132701945128</v>
       </c>
       <c r="DA7" t="n">
-        <v>0.02403452065468401</v>
+        <v>0.03266386854614258</v>
       </c>
       <c r="DB7" t="n">
         <v>0</v>
       </c>
       <c r="DC7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DD7" t="n">
         <v>0</v>
@@ -4171,52 +4171,52 @@
         <v>0</v>
       </c>
       <c r="DF7" t="n">
-        <v>0.01379199503545839</v>
+        <v>-0.04581506598461409</v>
       </c>
       <c r="DG7" t="n">
         <v>-0</v>
       </c>
       <c r="DH7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.0402431189041441</v>
+        <v>0.02136338692640853</v>
       </c>
       <c r="DJ7" t="n">
-        <v>0.008782646176267592</v>
+        <v>0.0051614560737841</v>
       </c>
       <c r="DK7" t="n">
         <v>0</v>
       </c>
       <c r="DL7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO7" t="n">
-        <v>-0.01565589696870085</v>
+        <v>-0.001109043840519018</v>
       </c>
       <c r="DP7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR7" t="n">
-        <v>0.02910626667383547</v>
+        <v>-0.04256569999230401</v>
       </c>
       <c r="DS7" t="n">
-        <v>-0.03707571895643469</v>
+        <v>-0.01078201880184573</v>
       </c>
       <c r="DT7" t="n">
         <v>-0</v>
       </c>
       <c r="DU7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DV7" t="n">
         <v>-0</v>
@@ -4225,7 +4225,7 @@
         <v>-0</v>
       </c>
       <c r="DX7" t="n">
-        <v>-0.0212144166455525</v>
+        <v>0.04754712355329607</v>
       </c>
       <c r="DY7" t="n">
         <v>0</v>
@@ -4234,43 +4234,43 @@
         <v>0</v>
       </c>
       <c r="EA7" t="n">
-        <v>-0.03257087521762704</v>
+        <v>-0.1199570425418499</v>
       </c>
       <c r="EB7" t="n">
-        <v>-0.008807449494598768</v>
+        <v>0.006107042299758373</v>
       </c>
       <c r="EC7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ED7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE7" t="n">
         <v>-0</v>
       </c>
       <c r="EF7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG7" t="n">
-        <v>-0.003804885509893497</v>
+        <v>0.0007389779837982684</v>
       </c>
       <c r="EH7" t="n">
         <v>-0</v>
       </c>
       <c r="EI7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ7" t="n">
-        <v>0.0008147869060856897</v>
+        <v>-0.0323024635691204</v>
       </c>
       <c r="EK7" t="n">
-        <v>0.01119724810717862</v>
+        <v>0.01513658435690808</v>
       </c>
       <c r="EL7" t="n">
         <v>-0</v>
       </c>
       <c r="EM7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN7" t="n">
         <v>-0</v>
@@ -4279,7 +4279,7 @@
         <v>0</v>
       </c>
       <c r="EP7" t="n">
-        <v>0.01248363226861039</v>
+        <v>-0.0102510539252018</v>
       </c>
       <c r="EQ7" t="n">
         <v>-0</v>
@@ -4288,25 +4288,25 @@
         <v>0</v>
       </c>
       <c r="ES7" t="n">
-        <v>0.007224120551593849</v>
+        <v>-0.09790804661857509</v>
       </c>
       <c r="ET7" t="n">
-        <v>0.02239737085752631</v>
+        <v>0.0417256410388657</v>
       </c>
       <c r="EU7" t="n">
         <v>0</v>
       </c>
       <c r="EV7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW7" t="n">
         <v>-0</v>
       </c>
       <c r="EX7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EY7" t="n">
-        <v>-0.002700783991081407</v>
+        <v>-0.06807301021869036</v>
       </c>
       <c r="EZ7" t="n">
         <v>-0</v>
@@ -4315,16 +4315,16 @@
         <v>0</v>
       </c>
       <c r="FB7" t="n">
-        <v>0.01215194106831204</v>
+        <v>0.01145061150957703</v>
       </c>
       <c r="FC7" t="n">
-        <v>0.02490946291845604</v>
+        <v>0.01643240446996149</v>
       </c>
       <c r="FD7" t="n">
         <v>-0</v>
       </c>
       <c r="FE7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FF7" t="n">
         <v>-0</v>
@@ -4333,19 +4333,19 @@
         <v>0</v>
       </c>
       <c r="FH7" t="n">
-        <v>-0.03921171515845626</v>
+        <v>-0.04406574774986601</v>
       </c>
       <c r="FI7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ7" t="n">
         <v>-0</v>
       </c>
       <c r="FK7" t="n">
-        <v>-0.03753146945002031</v>
+        <v>0.07942714233038937</v>
       </c>
       <c r="FL7" t="n">
-        <v>0.001672153112948349</v>
+        <v>-0.01094383966618348</v>
       </c>
       <c r="FM7" t="n">
         <v>0</v>
@@ -4357,37 +4357,37 @@
         <v>0</v>
       </c>
       <c r="FP7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ7" t="n">
-        <v>0.002549926538264363</v>
+        <v>0.01647305758025944</v>
       </c>
       <c r="FR7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS7" t="n">
         <v>-0</v>
       </c>
       <c r="FT7" t="n">
-        <v>0.0007760932560016291</v>
+        <v>-0.02476120400271552</v>
       </c>
       <c r="FU7" t="n">
-        <v>0.02263304643341775</v>
+        <v>-0.08692090468835134</v>
       </c>
       <c r="FV7" t="n">
         <v>-0</v>
       </c>
       <c r="FW7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ7" t="n">
-        <v>-0.01410530170105408</v>
+        <v>-0.05328057303612307</v>
       </c>
       <c r="GA7" t="n">
         <v>0</v>
@@ -4399,7 +4399,7 @@
         <v>-0</v>
       </c>
       <c r="GD7" t="n">
-        <v>-0.01215460077588423</v>
+        <v>0.03878470268949102</v>
       </c>
       <c r="GE7" t="n">
         <v>-0</v>
@@ -4408,7 +4408,7 @@
         <v>0</v>
       </c>
       <c r="GG7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="8">
@@ -4416,16 +4416,16 @@
         <v>0</v>
       </c>
       <c r="B8" t="n">
-        <v>0.2991655407023802</v>
+        <v>0.2043967359104011</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.1337146512228189</v>
+        <v>-0.0949020846936133</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.02299709676626816</v>
+        <v>-0.02684004820898313</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -4443,16 +4443,16 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1839923436496692</v>
+        <v>0.1743051004640752</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.08593101078037338</v>
+        <v>-0.07502730458844598</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.06842174153140412</v>
+        <v>-0.03992219489547777</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -4467,79 +4467,79 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>0.117137780611458</v>
+        <v>0.06893731482296027</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V8" t="n">
-        <v>0.02502427166676887</v>
+        <v>-0.04343401228521133</v>
       </c>
       <c r="W8" t="n">
-        <v>0.08246144596569417</v>
+        <v>-0.05244954210531854</v>
       </c>
       <c r="X8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA8" t="n">
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>-0.01436576256535797</v>
+        <v>0.0007481180998888366</v>
       </c>
       <c r="AD8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>-0.005069757269862143</v>
+        <v>0.03880144804050092</v>
       </c>
       <c r="AF8" t="n">
-        <v>-0.001987185075442475</v>
+        <v>0.01234770263200895</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
         <v>-0</v>
       </c>
       <c r="AJ8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK8" t="n">
         <v>0</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.05004790750357353</v>
+        <v>0.1178484828822538</v>
       </c>
       <c r="AM8" t="n">
         <v>0</v>
       </c>
       <c r="AN8" t="n">
-        <v>-0.05410458125643416</v>
+        <v>-0.04624503647429259</v>
       </c>
       <c r="AO8" t="n">
-        <v>-0.003514703508163365</v>
+        <v>0.06374866880020344</v>
       </c>
       <c r="AP8" t="n">
         <v>0</v>
       </c>
       <c r="AQ8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR8" t="n">
         <v>-0</v>
@@ -4548,19 +4548,19 @@
         <v>0</v>
       </c>
       <c r="AT8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.4541160972121623</v>
+        <v>0.2679973734042084</v>
       </c>
       <c r="AV8" t="n">
         <v>-0</v>
       </c>
       <c r="AW8" t="n">
-        <v>-2.964295790191198e-05</v>
+        <v>-0.08433754373844726</v>
       </c>
       <c r="AX8" t="n">
-        <v>0.1840954729446385</v>
+        <v>-0.1010656464615602</v>
       </c>
       <c r="AY8" t="n">
         <v>-0</v>
@@ -4578,16 +4578,16 @@
         <v>0</v>
       </c>
       <c r="BD8" t="n">
-        <v>-0.001903750711806942</v>
+        <v>-0.02719366872170031</v>
       </c>
       <c r="BE8" t="n">
         <v>0</v>
       </c>
       <c r="BF8" t="n">
-        <v>-0.1016204502870296</v>
+        <v>-0.03840401458163119</v>
       </c>
       <c r="BG8" t="n">
-        <v>-0.1775406041409951</v>
+        <v>-0.04370737301804205</v>
       </c>
       <c r="BH8" t="n">
         <v>0</v>
@@ -4596,7 +4596,7 @@
         <v>-0</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK8" t="n">
         <v>0</v>
@@ -4605,22 +4605,22 @@
         <v>-0</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.02623590385762304</v>
+        <v>0.007089188986577839</v>
       </c>
       <c r="BN8" t="n">
         <v>-0</v>
       </c>
       <c r="BO8" t="n">
-        <v>0.09738002006287601</v>
+        <v>0.01176587893985261</v>
       </c>
       <c r="BP8" t="n">
-        <v>0.04626640726310187</v>
+        <v>0.06743854254508218</v>
       </c>
       <c r="BQ8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS8" t="n">
         <v>-0</v>
@@ -4632,22 +4632,22 @@
         <v>-0</v>
       </c>
       <c r="BV8" t="n">
-        <v>0.264421529765111</v>
+        <v>0.2107451398223429</v>
       </c>
       <c r="BW8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX8" t="n">
-        <v>-0.02664429736729506</v>
+        <v>-0.08441043154880323</v>
       </c>
       <c r="BY8" t="n">
-        <v>0.06780480379153342</v>
+        <v>-0.04588139477240687</v>
       </c>
       <c r="BZ8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB8" t="n">
         <v>0</v>
@@ -4659,22 +4659,22 @@
         <v>-0</v>
       </c>
       <c r="CE8" t="n">
-        <v>-0.1001105262154275</v>
+        <v>-0.09430590232653069</v>
       </c>
       <c r="CF8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG8" t="n">
-        <v>0.03160734703885835</v>
+        <v>0.0805608262859939</v>
       </c>
       <c r="CH8" t="n">
-        <v>-0.02830436892055884</v>
+        <v>-0.009586890142181958</v>
       </c>
       <c r="CI8" t="n">
         <v>-0</v>
       </c>
       <c r="CJ8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK8" t="n">
         <v>0</v>
@@ -4686,19 +4686,19 @@
         <v>0</v>
       </c>
       <c r="CN8" t="n">
-        <v>-0.01737130702935192</v>
+        <v>-0.02968372333573732</v>
       </c>
       <c r="CO8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP8" t="n">
-        <v>-0.037384522195685</v>
+        <v>0.05776747950605818</v>
       </c>
       <c r="CQ8" t="n">
-        <v>-0.06689093543471411</v>
+        <v>0.01900649008040153</v>
       </c>
       <c r="CR8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS8" t="n">
         <v>-0</v>
@@ -4707,31 +4707,31 @@
         <v>-0</v>
       </c>
       <c r="CU8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV8" t="n">
         <v>0</v>
       </c>
       <c r="CW8" t="n">
-        <v>-0.08431333925097757</v>
+        <v>-0.08964673358549564</v>
       </c>
       <c r="CX8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY8" t="n">
-        <v>0.04815831367184555</v>
+        <v>0.0867821256430233</v>
       </c>
       <c r="CZ8" t="n">
-        <v>-0.02585486417813766</v>
+        <v>0.002740889426092844</v>
       </c>
       <c r="DA8" t="n">
         <v>0</v>
       </c>
       <c r="DB8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD8" t="n">
         <v>0</v>
@@ -4740,22 +4740,22 @@
         <v>0</v>
       </c>
       <c r="DF8" t="n">
-        <v>-0.03119238281215773</v>
+        <v>-0.05238185506423464</v>
       </c>
       <c r="DG8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH8" t="n">
-        <v>0.01844449692145412</v>
+        <v>0.02886261325246566</v>
       </c>
       <c r="DI8" t="n">
-        <v>0.01201402092322859</v>
+        <v>-0.05138360227469267</v>
       </c>
       <c r="DJ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL8" t="n">
         <v>0</v>
@@ -4767,22 +4767,22 @@
         <v>-0</v>
       </c>
       <c r="DO8" t="n">
-        <v>-0.05758240523988836</v>
+        <v>-0.06616548230904873</v>
       </c>
       <c r="DP8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ8" t="n">
-        <v>-0.01154626393068806</v>
+        <v>0.03801450832484579</v>
       </c>
       <c r="DR8" t="n">
-        <v>-0.05559416389747699</v>
+        <v>-0.01115781614093255</v>
       </c>
       <c r="DS8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DU8" t="n">
         <v>-0</v>
@@ -4791,25 +4791,25 @@
         <v>0</v>
       </c>
       <c r="DW8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX8" t="n">
-        <v>0.01951706208752055</v>
+        <v>0.06038556335754026</v>
       </c>
       <c r="DY8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ8" t="n">
-        <v>-0.0007021956513472662</v>
+        <v>-0.06797283431675213</v>
       </c>
       <c r="EA8" t="n">
-        <v>-0.04888902471596526</v>
+        <v>0.009309734594321812</v>
       </c>
       <c r="EB8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED8" t="n">
         <v>0</v>
@@ -4818,19 +4818,19 @@
         <v>-0</v>
       </c>
       <c r="EF8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG8" t="n">
-        <v>-0.05042778507558751</v>
+        <v>-0.04760953120743699</v>
       </c>
       <c r="EH8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI8" t="n">
-        <v>0.0500653182985264</v>
+        <v>0.05752150939899939</v>
       </c>
       <c r="EJ8" t="n">
-        <v>0.04048807480871891</v>
+        <v>-0.003216732262415074</v>
       </c>
       <c r="EK8" t="n">
         <v>-0</v>
@@ -4839,31 +4839,31 @@
         <v>-0</v>
       </c>
       <c r="EM8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO8" t="n">
         <v>0</v>
       </c>
       <c r="EP8" t="n">
-        <v>-0.09430482879500603</v>
+        <v>-0.03858136712995642</v>
       </c>
       <c r="EQ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER8" t="n">
-        <v>0.05351609423228395</v>
+        <v>0.05292445939326437</v>
       </c>
       <c r="ES8" t="n">
-        <v>-0.0238753540970365</v>
+        <v>-0.01703191313720392</v>
       </c>
       <c r="ET8" t="n">
         <v>-0</v>
       </c>
       <c r="EU8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV8" t="n">
         <v>0</v>
@@ -4875,25 +4875,25 @@
         <v>-0</v>
       </c>
       <c r="EY8" t="n">
-        <v>-0.09455324442575354</v>
+        <v>-0.1089520348528149</v>
       </c>
       <c r="EZ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA8" t="n">
-        <v>0.05833036685119738</v>
+        <v>0.08626022842386281</v>
       </c>
       <c r="FB8" t="n">
-        <v>-0.03323222152922791</v>
+        <v>-0.01272592562948865</v>
       </c>
       <c r="FC8" t="n">
         <v>-0</v>
       </c>
       <c r="FD8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF8" t="n">
         <v>-0</v>
@@ -4902,82 +4902,82 @@
         <v>-0</v>
       </c>
       <c r="FH8" t="n">
-        <v>-0.02353997643231373</v>
+        <v>-0.03189205906307055</v>
       </c>
       <c r="FI8" t="n">
         <v>-0</v>
       </c>
       <c r="FJ8" t="n">
-        <v>0.08446340901551409</v>
+        <v>0.02820668887242551</v>
       </c>
       <c r="FK8" t="n">
-        <v>-0.0596487194617159</v>
+        <v>-0.01720579925621216</v>
       </c>
       <c r="FL8" t="n">
         <v>-0</v>
       </c>
       <c r="FM8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN8" t="n">
         <v>0</v>
       </c>
       <c r="FO8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP8" t="n">
         <v>-0</v>
       </c>
       <c r="FQ8" t="n">
-        <v>0.004116256421288877</v>
+        <v>1.443971524271381e-05</v>
       </c>
       <c r="FR8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS8" t="n">
-        <v>0.03614379511815959</v>
+        <v>0.03735519532989307</v>
       </c>
       <c r="FT8" t="n">
-        <v>0.009029616755326443</v>
+        <v>-0.008091810182738714</v>
       </c>
       <c r="FU8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV8" t="n">
         <v>0</v>
       </c>
       <c r="FW8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX8" t="n">
         <v>0</v>
       </c>
       <c r="FY8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ8" t="n">
-        <v>-0.04575079795887849</v>
+        <v>-0.06006025916760033</v>
       </c>
       <c r="GA8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB8" t="n">
-        <v>-0.05253337324651499</v>
+        <v>0.02398499238845895</v>
       </c>
       <c r="GC8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE8" t="n">
         <v>-0</v>
       </c>
       <c r="GF8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -4985,19 +4985,19 @@
         <v>0</v>
       </c>
       <c r="B9" t="n">
-        <v>0.2016200698600772</v>
+        <v>0.4391836570460012</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.02828398123509208</v>
+        <v>-0.08508982128860217</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.093476946654628</v>
+        <v>-0.04914017460082042</v>
       </c>
       <c r="G9" t="n">
         <v>-0</v>
@@ -5012,25 +5012,25 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1189449628169975</v>
+        <v>0.4498051628418803</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.01830794669355592</v>
+        <v>-0.1444114818051923</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.09250080132163531</v>
+        <v>0.008909417787219367</v>
       </c>
       <c r="P9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -5039,7 +5039,7 @@
         <v>-0</v>
       </c>
       <c r="T9" t="n">
-        <v>0.02824378604627632</v>
+        <v>0.1366449784030271</v>
       </c>
       <c r="U9" t="n">
         <v>0</v>
@@ -5048,40 +5048,40 @@
         <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.03894487306704671</v>
+        <v>-0.04491740545718955</v>
       </c>
       <c r="X9" t="n">
-        <v>0.004610364034336885</v>
+        <v>0.02176032398668432</v>
       </c>
       <c r="Y9" t="n">
         <v>-0</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.691551441474009e-11</v>
+        <v>9.2939303637693e-12</v>
       </c>
       <c r="AD9" t="n">
         <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>-0.00596454300311594</v>
+        <v>0.02289470147832216</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.001115614581753533</v>
+        <v>0.0003813605235772281</v>
       </c>
       <c r="AH9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
         <v>-0</v>
@@ -5093,61 +5093,61 @@
         <v>0</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.02982804236953858</v>
+        <v>0.1459921179994578</v>
       </c>
       <c r="AM9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN9" t="n">
         <v>0</v>
       </c>
       <c r="AO9" t="n">
-        <v>-0.0236422119088574</v>
+        <v>0.04199398218999842</v>
       </c>
       <c r="AP9" t="n">
-        <v>-0.04961560411197791</v>
+        <v>-0.07621638299388205</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR9" t="n">
         <v>-0</v>
       </c>
       <c r="AS9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.2053924626296474</v>
+        <v>0.6355465242404554</v>
       </c>
       <c r="AV9" t="n">
         <v>-0</v>
       </c>
       <c r="AW9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AX9" t="n">
-        <v>-0.04747174988189866</v>
+        <v>-0.3034124278856554</v>
       </c>
       <c r="AY9" t="n">
-        <v>-0.1405075345496391</v>
+        <v>-0.1287873127909539</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC9" t="n">
         <v>0</v>
       </c>
       <c r="BD9" t="n">
-        <v>0.08181193603088736</v>
+        <v>0.02336974499488986</v>
       </c>
       <c r="BE9" t="n">
         <v>0</v>
@@ -5156,52 +5156,52 @@
         <v>0</v>
       </c>
       <c r="BG9" t="n">
-        <v>-0.0641620387399494</v>
+        <v>-0.09403302120323864</v>
       </c>
       <c r="BH9" t="n">
-        <v>-0.03965821041921416</v>
+        <v>-0.09220478604356878</v>
       </c>
       <c r="BI9" t="n">
         <v>-0</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.08986911072471838</v>
+        <v>0.03767160257010319</v>
       </c>
       <c r="BN9" t="n">
         <v>0</v>
       </c>
       <c r="BO9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BP9" t="n">
-        <v>0.03016374233478033</v>
+        <v>0.1219843057445905</v>
       </c>
       <c r="BQ9" t="n">
-        <v>0.01477799146924273</v>
+        <v>0.0003153103008546464</v>
       </c>
       <c r="BR9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BV9" t="n">
-        <v>0.09397567839318288</v>
+        <v>0.4768760297035938</v>
       </c>
       <c r="BW9" t="n">
         <v>0</v>
@@ -5210,10 +5210,10 @@
         <v>0</v>
       </c>
       <c r="BY9" t="n">
-        <v>-0.03407959780182785</v>
+        <v>-0.1085043593283578</v>
       </c>
       <c r="BZ9" t="n">
-        <v>-0.0393768491070457</v>
+        <v>-0.02484482540393315</v>
       </c>
       <c r="CA9" t="n">
         <v>-0</v>
@@ -5222,52 +5222,52 @@
         <v>-0</v>
       </c>
       <c r="CC9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CD9" t="n">
         <v>-0</v>
       </c>
       <c r="CE9" t="n">
-        <v>-0.05113751954914008</v>
+        <v>-0.2063759550346904</v>
       </c>
       <c r="CF9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG9" t="n">
         <v>-0</v>
       </c>
       <c r="CH9" t="n">
-        <v>-0.009894896601931205</v>
+        <v>0.05231067192970051</v>
       </c>
       <c r="CI9" t="n">
-        <v>0.04531000315862903</v>
+        <v>0.04411038463451633</v>
       </c>
       <c r="CJ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CL9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM9" t="n">
         <v>0</v>
       </c>
       <c r="CN9" t="n">
-        <v>0.002368845539271552</v>
+        <v>-0.1665254867856326</v>
       </c>
       <c r="CO9" t="n">
         <v>-0</v>
       </c>
       <c r="CP9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ9" t="n">
-        <v>0.0189845259326336</v>
+        <v>0.100269251333758</v>
       </c>
       <c r="CR9" t="n">
-        <v>-0.02421187464136875</v>
+        <v>0.07121834088412821</v>
       </c>
       <c r="CS9" t="n">
         <v>-0</v>
@@ -5276,31 +5276,31 @@
         <v>-0</v>
       </c>
       <c r="CU9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV9" t="n">
         <v>0</v>
       </c>
       <c r="CW9" t="n">
-        <v>-0.03752185554144535</v>
+        <v>-0.2086061898542815</v>
       </c>
       <c r="CX9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY9" t="n">
         <v>0</v>
       </c>
       <c r="CZ9" t="n">
-        <v>-0.00695691234982505</v>
+        <v>0.01367826864035084</v>
       </c>
       <c r="DA9" t="n">
-        <v>0.04544022101382912</v>
+        <v>0.04423160453456917</v>
       </c>
       <c r="DB9" t="n">
         <v>0</v>
       </c>
       <c r="DC9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DD9" t="n">
         <v>0</v>
@@ -5309,19 +5309,19 @@
         <v>0</v>
       </c>
       <c r="DF9" t="n">
-        <v>-0.02747934292126169</v>
+        <v>-0.05773860883406922</v>
       </c>
       <c r="DG9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH9" t="n">
         <v>-0</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.03831161589383129</v>
+        <v>-0.1402532165614136</v>
       </c>
       <c r="DJ9" t="n">
-        <v>-0.0009125582400060809</v>
+        <v>0.07170467473940187</v>
       </c>
       <c r="DK9" t="n">
         <v>0</v>
@@ -5333,37 +5333,37 @@
         <v>0</v>
       </c>
       <c r="DN9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO9" t="n">
-        <v>-0.009429958771049804</v>
+        <v>-0.07370340757190044</v>
       </c>
       <c r="DP9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR9" t="n">
-        <v>0.03099820871313516</v>
+        <v>0.02678859445318855</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.0073984208639212</v>
+        <v>-0.1033372409441351</v>
       </c>
       <c r="DT9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU9" t="n">
         <v>-0</v>
       </c>
       <c r="DV9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW9" t="n">
         <v>-0</v>
       </c>
       <c r="DX9" t="n">
-        <v>0.01863214377988351</v>
+        <v>0.08188556740968424</v>
       </c>
       <c r="DY9" t="n">
         <v>0</v>
@@ -5372,10 +5372,10 @@
         <v>0</v>
       </c>
       <c r="EA9" t="n">
-        <v>-0.04050466720513071</v>
+        <v>-0.0532092008435026</v>
       </c>
       <c r="EB9" t="n">
-        <v>-0.01457842066542181</v>
+        <v>-0.1456716993736504</v>
       </c>
       <c r="EC9" t="n">
         <v>-0</v>
@@ -5384,52 +5384,52 @@
         <v>0</v>
       </c>
       <c r="EE9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF9" t="n">
         <v>-0</v>
       </c>
       <c r="EG9" t="n">
-        <v>-0.03140130190672209</v>
+        <v>-0.03592294641599254</v>
       </c>
       <c r="EH9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ9" t="n">
-        <v>0.00960368669802197</v>
+        <v>-0.04911663450626339</v>
       </c>
       <c r="EK9" t="n">
-        <v>0.02702853309662062</v>
+        <v>0.01370608645188261</v>
       </c>
       <c r="EL9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN9" t="n">
         <v>-0</v>
       </c>
       <c r="EO9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP9" t="n">
-        <v>-0.02375412959873717</v>
+        <v>-0.08958099324429078</v>
       </c>
       <c r="EQ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER9" t="n">
         <v>-0</v>
       </c>
       <c r="ES9" t="n">
-        <v>-0.03470050526115607</v>
+        <v>-0.1777536378925133</v>
       </c>
       <c r="ET9" t="n">
-        <v>0.04996702273157796</v>
+        <v>0.1257493719369511</v>
       </c>
       <c r="EU9" t="n">
         <v>-0</v>
@@ -5444,34 +5444,34 @@
         <v>-0</v>
       </c>
       <c r="EY9" t="n">
-        <v>-0.03690741081945436</v>
+        <v>-0.2445006894000137</v>
       </c>
       <c r="EZ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA9" t="n">
         <v>-0</v>
       </c>
       <c r="FB9" t="n">
-        <v>-0.006069963984585531</v>
+        <v>0.01358980605136382</v>
       </c>
       <c r="FC9" t="n">
-        <v>0.05002354839415199</v>
+        <v>0.03857796863866768</v>
       </c>
       <c r="FD9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FF9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG9" t="n">
         <v>0</v>
       </c>
       <c r="FH9" t="n">
-        <v>-0.01820471162238919</v>
+        <v>-0.2292605880511934</v>
       </c>
       <c r="FI9" t="n">
         <v>-0</v>
@@ -5480,37 +5480,37 @@
         <v>-0</v>
       </c>
       <c r="FK9" t="n">
-        <v>-0.04635868609534036</v>
+        <v>0.1495391543142764</v>
       </c>
       <c r="FL9" t="n">
-        <v>0.03226432283862726</v>
+        <v>0.002229037224249439</v>
       </c>
       <c r="FM9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ9" t="n">
-        <v>0.0004644577552183731</v>
+        <v>0.006383417908645333</v>
       </c>
       <c r="FR9" t="n">
         <v>-0</v>
       </c>
       <c r="FS9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FT9" t="n">
-        <v>-0.0019883450550759</v>
+        <v>-0.01416379075973641</v>
       </c>
       <c r="FU9" t="n">
-        <v>0.04704722766647704</v>
+        <v>-0.01906188467697973</v>
       </c>
       <c r="FV9" t="n">
         <v>-0</v>
@@ -5519,31 +5519,31 @@
         <v>-0</v>
       </c>
       <c r="FX9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FY9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ9" t="n">
-        <v>-0.008989538139922041</v>
+        <v>-0.04655901647855113</v>
       </c>
       <c r="GA9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB9" t="n">
         <v>-0</v>
       </c>
       <c r="GC9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD9" t="n">
-        <v>-0.03879068526105035</v>
+        <v>-0.04276739654721685</v>
       </c>
       <c r="GE9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GF9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG9" t="n">
         <v>0</v>
@@ -5554,16 +5554,16 @@
         <v>0</v>
       </c>
       <c r="B10" t="n">
-        <v>0.4276378345696668</v>
+        <v>0.215176791187576</v>
       </c>
       <c r="C10" t="n">
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.1223507126640145</v>
+        <v>-0.09880577099877545</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.09274972772962621</v>
+        <v>-0.009835843384622503</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
@@ -5581,16 +5581,16 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0.2374561594569027</v>
+        <v>0.1863136312215709</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.08457008416748373</v>
+        <v>-0.08944957572091236</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.08378973693320395</v>
+        <v>-0.03572015929583347</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -5608,70 +5608,70 @@
         <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>0.1418384045500858</v>
+        <v>0.06223246206612323</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.03322396377213294</v>
+        <v>-0.03511302823207119</v>
       </c>
       <c r="W10" t="n">
-        <v>0.03514293660941587</v>
+        <v>-0.04389238731833914</v>
       </c>
       <c r="X10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
         <v>-0</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA10" t="n">
         <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.00841518427963764</v>
+        <v>-0.006265991577692414</v>
       </c>
       <c r="AD10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.001170446524763154</v>
+        <v>0.01200430051900519</v>
       </c>
       <c r="AF10" t="n">
-        <v>-4.810277588416745e-12</v>
+        <v>-1.921930194461703e-11</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
         <v>0</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.06935365403228896</v>
+        <v>0.08170606702481249</v>
       </c>
       <c r="AM10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN10" t="n">
-        <v>-0.04402459861793503</v>
+        <v>-0.0143532004651838</v>
       </c>
       <c r="AO10" t="n">
-        <v>-0.04935057254580204</v>
+        <v>0.07382414694352955</v>
       </c>
       <c r="AP10" t="n">
         <v>0</v>
@@ -5680,52 +5680,52 @@
         <v>-0</v>
       </c>
       <c r="AR10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS10" t="n">
         <v>0</v>
       </c>
       <c r="AT10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.4842103436601837</v>
+        <v>0.2525401605173613</v>
       </c>
       <c r="AV10" t="n">
         <v>-0</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.009205589998771548</v>
+        <v>-0.04648327323476784</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.04444574416860191</v>
+        <v>-0.09087175398397547</v>
       </c>
       <c r="AY10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ10" t="n">
         <v>-0</v>
       </c>
       <c r="BA10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC10" t="n">
         <v>0</v>
       </c>
       <c r="BD10" t="n">
-        <v>0.02832854691686902</v>
+        <v>-0.02557047272195237</v>
       </c>
       <c r="BE10" t="n">
         <v>0</v>
       </c>
       <c r="BF10" t="n">
-        <v>-0.09531114137960292</v>
+        <v>-0.05562615308713571</v>
       </c>
       <c r="BG10" t="n">
-        <v>-0.1804283648762729</v>
+        <v>-0.04717510776866266</v>
       </c>
       <c r="BH10" t="n">
         <v>0</v>
@@ -5734,31 +5734,31 @@
         <v>-0</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK10" t="n">
         <v>0</v>
       </c>
       <c r="BL10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.0596928543597742</v>
+        <v>-0.01212443296714195</v>
       </c>
       <c r="BN10" t="n">
         <v>-0</v>
       </c>
       <c r="BO10" t="n">
-        <v>0.06595474396417451</v>
+        <v>0.01139428616321451</v>
       </c>
       <c r="BP10" t="n">
-        <v>0.09532891453456015</v>
+        <v>0.04302270763626223</v>
       </c>
       <c r="BQ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS10" t="n">
         <v>-0</v>
@@ -5767,46 +5767,46 @@
         <v>-0</v>
       </c>
       <c r="BU10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV10" t="n">
-        <v>0.259235886799352</v>
+        <v>0.1828962224764564</v>
       </c>
       <c r="BW10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX10" t="n">
-        <v>0.004290063503488106</v>
+        <v>-0.05820598001736919</v>
       </c>
       <c r="BY10" t="n">
-        <v>0.01116483425854476</v>
+        <v>-0.02766311625390743</v>
       </c>
       <c r="BZ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA10" t="n">
         <v>-0</v>
       </c>
       <c r="CB10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CE10" t="n">
-        <v>-0.1172551747268193</v>
+        <v>-0.09016600846078295</v>
       </c>
       <c r="CF10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG10" t="n">
-        <v>0.01250850604259887</v>
+        <v>0.05996387093306769</v>
       </c>
       <c r="CH10" t="n">
-        <v>-0.01210689147631779</v>
+        <v>-0.007486903939642986</v>
       </c>
       <c r="CI10" t="n">
         <v>-0</v>
@@ -5818,25 +5818,25 @@
         <v>0</v>
       </c>
       <c r="CL10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM10" t="n">
         <v>0</v>
       </c>
       <c r="CN10" t="n">
-        <v>0.004033865013187208</v>
+        <v>-0.02829647201106586</v>
       </c>
       <c r="CO10" t="n">
         <v>-0</v>
       </c>
       <c r="CP10" t="n">
-        <v>-0.04528262262292292</v>
+        <v>0.05168892094370017</v>
       </c>
       <c r="CQ10" t="n">
-        <v>-0.05698896555797917</v>
+        <v>0.02801846296154127</v>
       </c>
       <c r="CR10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS10" t="n">
         <v>-0</v>
@@ -5845,22 +5845,22 @@
         <v>-0</v>
       </c>
       <c r="CU10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW10" t="n">
-        <v>-0.1050262096880169</v>
+        <v>-0.0903142377521082</v>
       </c>
       <c r="CX10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY10" t="n">
-        <v>0.03592899918116428</v>
+        <v>0.06166024755433461</v>
       </c>
       <c r="CZ10" t="n">
-        <v>-0.02320402213778393</v>
+        <v>9.018583693443596e-05</v>
       </c>
       <c r="DA10" t="n">
         <v>0</v>
@@ -5878,16 +5878,16 @@
         <v>0</v>
       </c>
       <c r="DF10" t="n">
-        <v>-0.04990052378956466</v>
+        <v>-0.05040152489891466</v>
       </c>
       <c r="DG10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH10" t="n">
-        <v>0.02493285043983889</v>
+        <v>0.01380174321711892</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.06153394930765179</v>
+        <v>-0.06614500678656909</v>
       </c>
       <c r="DJ10" t="n">
         <v>-0</v>
@@ -5902,22 +5902,22 @@
         <v>0</v>
       </c>
       <c r="DN10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO10" t="n">
-        <v>-0.05102214943547478</v>
+        <v>-0.04606134897245883</v>
       </c>
       <c r="DP10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ10" t="n">
-        <v>0.04006774378769166</v>
+        <v>-0.01240381986159401</v>
       </c>
       <c r="DR10" t="n">
-        <v>-0.07186555698709439</v>
+        <v>-0.03497074772202745</v>
       </c>
       <c r="DS10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT10" t="n">
         <v>-0</v>
@@ -5929,55 +5929,55 @@
         <v>0</v>
       </c>
       <c r="DW10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX10" t="n">
-        <v>0.05357365311786155</v>
+        <v>0.07051976659857891</v>
       </c>
       <c r="DY10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ10" t="n">
-        <v>-0.002900978960051612</v>
+        <v>0.03542106414167833</v>
       </c>
       <c r="EA10" t="n">
-        <v>-0.08653359274526179</v>
+        <v>-0.007018884144948656</v>
       </c>
       <c r="EB10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED10" t="n">
         <v>0</v>
       </c>
       <c r="EE10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF10" t="n">
         <v>0</v>
       </c>
       <c r="EG10" t="n">
-        <v>-0.08424652573747646</v>
+        <v>-0.06490971423011978</v>
       </c>
       <c r="EH10" t="n">
         <v>-0</v>
       </c>
       <c r="EI10" t="n">
-        <v>0.03615595301540348</v>
+        <v>0.04587724526888578</v>
       </c>
       <c r="EJ10" t="n">
-        <v>0.03789917323532167</v>
+        <v>0.01425637932910143</v>
       </c>
       <c r="EK10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EL10" t="n">
         <v>-0</v>
       </c>
       <c r="EM10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN10" t="n">
         <v>-0</v>
@@ -5986,22 +5986,22 @@
         <v>0</v>
       </c>
       <c r="EP10" t="n">
-        <v>-0.05925220005919641</v>
+        <v>-0.02096324077463897</v>
       </c>
       <c r="EQ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER10" t="n">
-        <v>0.02713279867202972</v>
+        <v>0.04395551149221002</v>
       </c>
       <c r="ES10" t="n">
-        <v>-0.01901520248435236</v>
+        <v>-0.04002660525836276</v>
       </c>
       <c r="ET10" t="n">
         <v>-0</v>
       </c>
       <c r="EU10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV10" t="n">
         <v>0</v>
@@ -6013,16 +6013,16 @@
         <v>0</v>
       </c>
       <c r="EY10" t="n">
-        <v>-0.1032670699923739</v>
+        <v>-0.1043313682411442</v>
       </c>
       <c r="EZ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA10" t="n">
-        <v>0.02590303792982505</v>
+        <v>0.07416109583882104</v>
       </c>
       <c r="FB10" t="n">
-        <v>-0.01086064591378052</v>
+        <v>-0.01633240466378425</v>
       </c>
       <c r="FC10" t="n">
         <v>-0</v>
@@ -6034,88 +6034,88 @@
         <v>0</v>
       </c>
       <c r="FF10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG10" t="n">
         <v>0</v>
       </c>
       <c r="FH10" t="n">
-        <v>-0.03154296515638236</v>
+        <v>-0.04886791887192634</v>
       </c>
       <c r="FI10" t="n">
         <v>-0</v>
       </c>
       <c r="FJ10" t="n">
-        <v>0.06129344796235976</v>
+        <v>0.05079118801856696</v>
       </c>
       <c r="FK10" t="n">
-        <v>-0.03784809052241488</v>
+        <v>0.001460412195735367</v>
       </c>
       <c r="FL10" t="n">
         <v>-0</v>
       </c>
       <c r="FM10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN10" t="n">
         <v>-0</v>
       </c>
       <c r="FO10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ10" t="n">
-        <v>0.0003217106393567314</v>
+        <v>0.000753068587597473</v>
       </c>
       <c r="FR10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS10" t="n">
-        <v>0.04500084995298304</v>
+        <v>0.09943469232752083</v>
       </c>
       <c r="FT10" t="n">
-        <v>-0.001612778113970357</v>
+        <v>-0.003186509615539856</v>
       </c>
       <c r="FU10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX10" t="n">
         <v>0</v>
       </c>
       <c r="FY10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ10" t="n">
-        <v>-0.002771957034404669</v>
+        <v>-0.06470740915581281</v>
       </c>
       <c r="GA10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB10" t="n">
-        <v>-0.04754024118900892</v>
+        <v>0.02328585993141171</v>
       </c>
       <c r="GC10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE10" t="n">
         <v>-0</v>
       </c>
       <c r="GF10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -6123,22 +6123,22 @@
         <v>0</v>
       </c>
       <c r="B11" t="n">
-        <v>0.6978032179285124</v>
+        <v>0.4618567568589058</v>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.09145286874785845</v>
+        <v>0.1556316082468717</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.5473317535429933</v>
+        <v>-0.230597106604367</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H11" t="n">
         <v>-0</v>
@@ -6150,25 +6150,25 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0.4538211960776657</v>
+        <v>0.5213580740270962</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.0008296824976469492</v>
+        <v>0.07708620278133939</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.4862045562546478</v>
+        <v>-0.1495837727597333</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -6177,25 +6177,25 @@
         <v>-0</v>
       </c>
       <c r="T11" t="n">
-        <v>0.1063009476826921</v>
+        <v>0.1759876128450722</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.1330875734042448</v>
+        <v>-0.1619941027260955</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.02742007848276714</v>
+        <v>-0.003568871154450517</v>
       </c>
       <c r="Y11" t="n">
         <v>-0</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>
@@ -6204,34 +6204,34 @@
         <v>-0</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.02071549529852219</v>
+        <v>0.0131065251673159</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AE11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>-0.001666058039023525</v>
+        <v>-0.04726723024818994</v>
       </c>
       <c r="AG11" t="n">
-        <v>-0.003512144507694994</v>
+        <v>-0.03220018633199308</v>
       </c>
       <c r="AH11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
         <v>-0</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AK11" t="n">
         <v>0</v>
       </c>
       <c r="AL11" t="n">
-        <v>0.1374966727345234</v>
+        <v>0.1622287377137854</v>
       </c>
       <c r="AM11" t="n">
         <v>0</v>
@@ -6240,13 +6240,13 @@
         <v>0</v>
       </c>
       <c r="AO11" t="n">
-        <v>0.07727660725570855</v>
+        <v>-0.02012072231834464</v>
       </c>
       <c r="AP11" t="n">
-        <v>-0.1423010454176762</v>
+        <v>-0.339496060061484</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR11" t="n">
         <v>-0</v>
@@ -6255,37 +6255,37 @@
         <v>0</v>
       </c>
       <c r="AT11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU11" t="n">
-        <v>0.6549866756384572</v>
+        <v>0.9698866186835086</v>
       </c>
       <c r="AV11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW11" t="n">
         <v>0</v>
       </c>
       <c r="AX11" t="n">
-        <v>-0.1651416492330452</v>
+        <v>-0.02452456970557832</v>
       </c>
       <c r="AY11" t="n">
-        <v>-0.5545232963115215</v>
+        <v>-0.2504018251513472</v>
       </c>
       <c r="AZ11" t="n">
         <v>0</v>
       </c>
       <c r="BA11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD11" t="n">
-        <v>0.2426433557524847</v>
+        <v>-0.1493024056538699</v>
       </c>
       <c r="BE11" t="n">
         <v>0</v>
@@ -6294,16 +6294,16 @@
         <v>0</v>
       </c>
       <c r="BG11" t="n">
-        <v>-0.1176364376556842</v>
+        <v>-0.2290012261110196</v>
       </c>
       <c r="BH11" t="n">
-        <v>-0.1464355380560577</v>
+        <v>-0.2879128012751396</v>
       </c>
       <c r="BI11" t="n">
         <v>-0</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK11" t="n">
         <v>0</v>
@@ -6312,46 +6312,46 @@
         <v>-0</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.1749275417453558</v>
+        <v>0.2099660868597128</v>
       </c>
       <c r="BN11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO11" t="n">
         <v>-0</v>
       </c>
       <c r="BP11" t="n">
-        <v>0.00764741736507042</v>
+        <v>0.2722368149212764</v>
       </c>
       <c r="BQ11" t="n">
-        <v>-0.01870142755336184</v>
+        <v>-0.00819914207233396</v>
       </c>
       <c r="BR11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS11" t="n">
         <v>0</v>
       </c>
       <c r="BT11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BU11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BV11" t="n">
-        <v>0.3474093759755273</v>
+        <v>0.5559519703002301</v>
       </c>
       <c r="BW11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX11" t="n">
         <v>0</v>
       </c>
       <c r="BY11" t="n">
-        <v>-0.1121487166549322</v>
+        <v>-0.02767987554554309</v>
       </c>
       <c r="BZ11" t="n">
-        <v>-0.3410209577663225</v>
+        <v>-0.2171182799321633</v>
       </c>
       <c r="CA11" t="n">
         <v>-0</v>
@@ -6366,49 +6366,49 @@
         <v>-0</v>
       </c>
       <c r="CE11" t="n">
-        <v>-0.1445299467474491</v>
+        <v>-0.2201587579679619</v>
       </c>
       <c r="CF11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG11" t="n">
         <v>-0</v>
       </c>
       <c r="CH11" t="n">
-        <v>-0.04502212445227508</v>
+        <v>0.03117524235855131</v>
       </c>
       <c r="CI11" t="n">
-        <v>0.1499724780201077</v>
+        <v>0.08872657189684888</v>
       </c>
       <c r="CJ11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK11" t="n">
         <v>0</v>
       </c>
       <c r="CL11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM11" t="n">
         <v>0</v>
       </c>
       <c r="CN11" t="n">
-        <v>-0.004856304560014615</v>
+        <v>-0.233323209546896</v>
       </c>
       <c r="CO11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CP11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ11" t="n">
-        <v>0.01002676708294641</v>
+        <v>0.1216924187833671</v>
       </c>
       <c r="CR11" t="n">
-        <v>-0.001905239557424849</v>
+        <v>0.1679862676525474</v>
       </c>
       <c r="CS11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT11" t="n">
         <v>-0</v>
@@ -6417,106 +6417,106 @@
         <v>-0</v>
       </c>
       <c r="CV11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW11" t="n">
-        <v>-0.1282484693401537</v>
+        <v>-0.2143715151691795</v>
       </c>
       <c r="CX11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY11" t="n">
         <v>0</v>
       </c>
       <c r="CZ11" t="n">
-        <v>-0.03020735698959942</v>
+        <v>-0.06202740739618503</v>
       </c>
       <c r="DA11" t="n">
-        <v>0.1661893890804487</v>
+        <v>0.07494378744368609</v>
       </c>
       <c r="DB11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC11" t="n">
         <v>-0</v>
       </c>
       <c r="DD11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DF11" t="n">
-        <v>-0.01007562483497726</v>
+        <v>-0.08344251251312478</v>
       </c>
       <c r="DG11" t="n">
         <v>0</v>
       </c>
       <c r="DH11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.08731376121461579</v>
+        <v>-0.1611252217562867</v>
       </c>
       <c r="DJ11" t="n">
-        <v>-0.07081805182404902</v>
+        <v>0.1472923205350554</v>
       </c>
       <c r="DK11" t="n">
         <v>0</v>
       </c>
       <c r="DL11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DM11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN11" t="n">
         <v>0</v>
       </c>
       <c r="DO11" t="n">
-        <v>-0.01593281808761119</v>
+        <v>-0.02293234688064223</v>
       </c>
       <c r="DP11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR11" t="n">
-        <v>-0.05756649719888268</v>
+        <v>-0.1063016941884297</v>
       </c>
       <c r="DS11" t="n">
-        <v>-0.0207653187582004</v>
+        <v>-0.01204892994865897</v>
       </c>
       <c r="DT11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DU11" t="n">
         <v>-0</v>
       </c>
       <c r="DV11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW11" t="n">
         <v>-0</v>
       </c>
       <c r="DX11" t="n">
-        <v>0.0152035387525668</v>
+        <v>0.1155057827504603</v>
       </c>
       <c r="DY11" t="n">
         <v>0</v>
       </c>
       <c r="DZ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA11" t="n">
-        <v>5.832767895188508e-05</v>
+        <v>-0.06786073097017511</v>
       </c>
       <c r="EB11" t="n">
-        <v>0.1060089535059511</v>
+        <v>0.01199613276865871</v>
       </c>
       <c r="EC11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED11" t="n">
         <v>0</v>
@@ -6525,64 +6525,64 @@
         <v>-0</v>
       </c>
       <c r="EF11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG11" t="n">
-        <v>-0.1213068607654178</v>
+        <v>-0.0491444843831047</v>
       </c>
       <c r="EH11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI11" t="n">
         <v>-0</v>
       </c>
       <c r="EJ11" t="n">
-        <v>0.03331831273797501</v>
+        <v>-0.1481529448100958</v>
       </c>
       <c r="EK11" t="n">
-        <v>0.1988546160261594</v>
+        <v>-0.09077453664789174</v>
       </c>
       <c r="EL11" t="n">
         <v>-0</v>
       </c>
       <c r="EM11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP11" t="n">
-        <v>-0.03672570348177021</v>
+        <v>-0.03179641277188492</v>
       </c>
       <c r="EQ11" t="n">
         <v>0</v>
       </c>
       <c r="ER11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ES11" t="n">
-        <v>-0.02389742029759002</v>
+        <v>-0.1796843712173906</v>
       </c>
       <c r="ET11" t="n">
-        <v>0.1114687156625804</v>
+        <v>0.2157168454877746</v>
       </c>
       <c r="EU11" t="n">
         <v>-0</v>
       </c>
       <c r="EV11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY11" t="n">
-        <v>-0.1064946187477862</v>
+        <v>-0.2483352332527632</v>
       </c>
       <c r="EZ11" t="n">
         <v>0</v>
@@ -6591,25 +6591,25 @@
         <v>-0</v>
       </c>
       <c r="FB11" t="n">
-        <v>-0.03472623908069158</v>
+        <v>-0.07751050687238321</v>
       </c>
       <c r="FC11" t="n">
-        <v>0.1325676786808672</v>
+        <v>0.0801869241605066</v>
       </c>
       <c r="FD11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE11" t="n">
         <v>0</v>
       </c>
       <c r="FF11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH11" t="n">
-        <v>-0.1269173624621555</v>
+        <v>-0.2912205092303803</v>
       </c>
       <c r="FI11" t="n">
         <v>-0</v>
@@ -6618,25 +6618,25 @@
         <v>-0</v>
       </c>
       <c r="FK11" t="n">
-        <v>0.0001795176839315643</v>
+        <v>0.183497760030153</v>
       </c>
       <c r="FL11" t="n">
-        <v>-0.0561612210239878</v>
+        <v>-0.1695799877404228</v>
       </c>
       <c r="FM11" t="n">
         <v>0</v>
       </c>
       <c r="FN11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO11" t="n">
         <v>0</v>
       </c>
       <c r="FP11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ11" t="n">
-        <v>-0.03258861221951262</v>
+        <v>-0.04274731669365319</v>
       </c>
       <c r="FR11" t="n">
         <v>-0</v>
@@ -6645,10 +6645,10 @@
         <v>-0</v>
       </c>
       <c r="FT11" t="n">
-        <v>0.0005416318334794538</v>
+        <v>0.0004935396728289713</v>
       </c>
       <c r="FU11" t="n">
-        <v>0.1001160441774091</v>
+        <v>0.01873285892276799</v>
       </c>
       <c r="FV11" t="n">
         <v>-0</v>
@@ -6660,22 +6660,22 @@
         <v>-0</v>
       </c>
       <c r="FY11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ11" t="n">
-        <v>0.05925516016867644</v>
+        <v>-0.04621033966584451</v>
       </c>
       <c r="GA11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GC11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD11" t="n">
-        <v>-0.04545495942012884</v>
+        <v>-0.06944857488638731</v>
       </c>
       <c r="GE11" t="n">
         <v>-0</v>
@@ -6684,24 +6684,24 @@
         <v>0</v>
       </c>
       <c r="GG11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>-0.1597295101346946</v>
+        <v>-0.2350798510099993</v>
       </c>
       <c r="B12" t="n">
-        <v>0.7208607689634069</v>
+        <v>0.3733419194737823</v>
       </c>
       <c r="C12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.1311540645967007</v>
+        <v>-0.02999185928066346</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -6716,10 +6716,10 @@
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.1777040369215677</v>
+        <v>-0.1910669840215216</v>
       </c>
       <c r="K12" t="n">
-        <v>0.496761257991638</v>
+        <v>0.4555599127935183</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -6728,10 +6728,10 @@
         <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.1804447453147433</v>
+        <v>-0.02187652184499298</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P12" t="n">
         <v>0</v>
@@ -6743,19 +6743,19 @@
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>0.06416780642212311</v>
+        <v>0.07113082520135237</v>
       </c>
       <c r="T12" t="n">
-        <v>0.2586550182507845</v>
+        <v>0.04363923236413327</v>
       </c>
       <c r="U12" t="n">
         <v>-0</v>
       </c>
       <c r="V12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.07038604805863656</v>
+        <v>-0.3067047431672854</v>
       </c>
       <c r="X12" t="n">
         <v>-0</v>
@@ -6764,70 +6764,70 @@
         <v>-0</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA12" t="n">
         <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.02134732566723702</v>
+        <v>0.01063582686989406</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.05680650224994011</v>
+        <v>0.03374850084838599</v>
       </c>
       <c r="AD12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>-0.02130214759116131</v>
+        <v>-0.1048288959831309</v>
       </c>
       <c r="AG12" t="n">
         <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
         <v>-0</v>
       </c>
       <c r="AJ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>-0.1175580452029755</v>
+        <v>-0.02695254220480019</v>
       </c>
       <c r="AL12" t="n">
-        <v>0.2001080270932497</v>
+        <v>0.1567987443936463</v>
       </c>
       <c r="AM12" t="n">
         <v>0</v>
       </c>
       <c r="AN12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO12" t="n">
-        <v>-0.02409936967436522</v>
+        <v>-0.2532604736740499</v>
       </c>
       <c r="AP12" t="n">
         <v>0</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AS12" t="n">
         <v>0</v>
       </c>
       <c r="AT12" t="n">
-        <v>0.03476605464245076</v>
+        <v>-0.1917771897689316</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.7609134649152516</v>
+        <v>0.3556741178419724</v>
       </c>
       <c r="AV12" t="n">
         <v>-0</v>
@@ -6836,25 +6836,25 @@
         <v>-0</v>
       </c>
       <c r="AX12" t="n">
-        <v>0.2313744765656061</v>
+        <v>-0.2857536676661178</v>
       </c>
       <c r="AY12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AZ12" t="n">
         <v>0</v>
       </c>
       <c r="BA12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC12" t="n">
-        <v>-0.0178545857258698</v>
+        <v>0.07645226937279812</v>
       </c>
       <c r="BD12" t="n">
-        <v>0.06017383152495609</v>
+        <v>0.2092304074650881</v>
       </c>
       <c r="BE12" t="n">
         <v>0</v>
@@ -6863,25 +6863,25 @@
         <v>0</v>
       </c>
       <c r="BG12" t="n">
-        <v>-0.3686101299932615</v>
+        <v>0.1532718467374858</v>
       </c>
       <c r="BH12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BI12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.0729114899759707</v>
+        <v>-0.05733573728563787</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.09749495498369305</v>
+        <v>0.1357387366570186</v>
       </c>
       <c r="BN12" t="n">
         <v>-0</v>
@@ -6890,7 +6890,7 @@
         <v>-0</v>
       </c>
       <c r="BP12" t="n">
-        <v>0.179276692209445</v>
+        <v>0.3267857535048249</v>
       </c>
       <c r="BQ12" t="n">
         <v>-0</v>
@@ -6905,19 +6905,19 @@
         <v>-0</v>
       </c>
       <c r="BU12" t="n">
-        <v>0.05567897735306023</v>
+        <v>-0.04471390418081681</v>
       </c>
       <c r="BV12" t="n">
-        <v>0.4999824174845359</v>
+        <v>0.2015048731350838</v>
       </c>
       <c r="BW12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX12" t="n">
         <v>0</v>
       </c>
       <c r="BY12" t="n">
-        <v>0.05620925953996862</v>
+        <v>-0.1618769061879499</v>
       </c>
       <c r="BZ12" t="n">
         <v>0</v>
@@ -6932,22 +6932,22 @@
         <v>0</v>
       </c>
       <c r="CD12" t="n">
-        <v>0.02844948005932978</v>
+        <v>0.1191834460630929</v>
       </c>
       <c r="CE12" t="n">
-        <v>-0.1444327768176717</v>
+        <v>-0.1059175874005382</v>
       </c>
       <c r="CF12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG12" t="n">
         <v>-0</v>
       </c>
       <c r="CH12" t="n">
-        <v>-0.001024914879042613</v>
+        <v>0.03672595008401254</v>
       </c>
       <c r="CI12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ12" t="n">
         <v>-0</v>
@@ -6959,46 +6959,46 @@
         <v>-0</v>
       </c>
       <c r="CM12" t="n">
-        <v>-0.1472885986088425</v>
+        <v>-0.003750226054602404</v>
       </c>
       <c r="CN12" t="n">
-        <v>-0.03526952816535919</v>
+        <v>-0.1374164527893902</v>
       </c>
       <c r="CO12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CP12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ12" t="n">
-        <v>-0.0991616076550899</v>
+        <v>-0.004856936587516581</v>
       </c>
       <c r="CR12" t="n">
         <v>-0</v>
       </c>
       <c r="CS12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT12" t="n">
         <v>-0</v>
       </c>
       <c r="CU12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV12" t="n">
-        <v>0.03194440099859026</v>
+        <v>0.104732202510157</v>
       </c>
       <c r="CW12" t="n">
-        <v>-0.1550081383786215</v>
+        <v>-0.106653290444367</v>
       </c>
       <c r="CX12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY12" t="n">
         <v>0</v>
       </c>
       <c r="CZ12" t="n">
-        <v>-0.002430681438214793</v>
+        <v>0.00830644455577231</v>
       </c>
       <c r="DA12" t="n">
         <v>0</v>
@@ -7013,19 +7013,19 @@
         <v>0</v>
       </c>
       <c r="DE12" t="n">
-        <v>-0.05439731513231223</v>
+        <v>0.06864574082222241</v>
       </c>
       <c r="DF12" t="n">
-        <v>-0.2349729389476932</v>
+        <v>0.004704433165688231</v>
       </c>
       <c r="DG12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.06345698440861149</v>
+        <v>-0.1058838623817021</v>
       </c>
       <c r="DJ12" t="n">
         <v>0</v>
@@ -7037,13 +7037,13 @@
         <v>0</v>
       </c>
       <c r="DM12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN12" t="n">
-        <v>-0.01191079417127548</v>
+        <v>0.06925211957714213</v>
       </c>
       <c r="DO12" t="n">
-        <v>-0.09272862965231134</v>
+        <v>-0.2068848883761303</v>
       </c>
       <c r="DP12" t="n">
         <v>-0</v>
@@ -7052,34 +7052,34 @@
         <v>-0</v>
       </c>
       <c r="DR12" t="n">
-        <v>-0.01348460346902835</v>
+        <v>-0.04302429135503431</v>
       </c>
       <c r="DS12" t="n">
         <v>-0</v>
       </c>
       <c r="DT12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU12" t="n">
         <v>-0</v>
       </c>
       <c r="DV12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW12" t="n">
-        <v>-0.009622393268151183</v>
+        <v>-0.09170002553929782</v>
       </c>
       <c r="DX12" t="n">
-        <v>-0.23093186616324</v>
+        <v>-0.2573520157549121</v>
       </c>
       <c r="DY12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA12" t="n">
-        <v>-0.1627950241500002</v>
+        <v>-0.1639790215527568</v>
       </c>
       <c r="EB12" t="n">
         <v>0</v>
@@ -7094,10 +7094,10 @@
         <v>-0</v>
       </c>
       <c r="EF12" t="n">
-        <v>-0.008625547671476816</v>
+        <v>0.09499926962314208</v>
       </c>
       <c r="EG12" t="n">
-        <v>-0.01442464024112438</v>
+        <v>0.03212634782788835</v>
       </c>
       <c r="EH12" t="n">
         <v>-0</v>
@@ -7106,10 +7106,10 @@
         <v>0</v>
       </c>
       <c r="EJ12" t="n">
-        <v>0.01235833763346941</v>
+        <v>-0.05292743751187682</v>
       </c>
       <c r="EK12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL12" t="n">
         <v>-0</v>
@@ -7121,19 +7121,19 @@
         <v>-0</v>
       </c>
       <c r="EO12" t="n">
-        <v>0.01588947982140381</v>
+        <v>0.06168060570680697</v>
       </c>
       <c r="EP12" t="n">
-        <v>-0.09907510956287283</v>
+        <v>-0.00520182688601106</v>
       </c>
       <c r="EQ12" t="n">
         <v>0</v>
       </c>
       <c r="ER12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ES12" t="n">
-        <v>-0.1107981985349412</v>
+        <v>0.02073390217067779</v>
       </c>
       <c r="ET12" t="n">
         <v>-0</v>
@@ -7145,13 +7145,13 @@
         <v>0</v>
       </c>
       <c r="EW12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX12" t="n">
-        <v>0.02790737317017221</v>
+        <v>0.1280953283701283</v>
       </c>
       <c r="EY12" t="n">
-        <v>-0.1468139214737703</v>
+        <v>-0.135554763498388</v>
       </c>
       <c r="EZ12" t="n">
         <v>-0</v>
@@ -7160,7 +7160,7 @@
         <v>-0</v>
       </c>
       <c r="FB12" t="n">
-        <v>-0.03974007332914726</v>
+        <v>0.0004497412680718695</v>
       </c>
       <c r="FC12" t="n">
         <v>-0</v>
@@ -7172,28 +7172,28 @@
         <v>0</v>
       </c>
       <c r="FF12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG12" t="n">
-        <v>0.0249180591828504</v>
+        <v>-0.01604365059442664</v>
       </c>
       <c r="FH12" t="n">
-        <v>-0.04617949353482961</v>
+        <v>-0.1554684086127929</v>
       </c>
       <c r="FI12" t="n">
         <v>-0</v>
       </c>
       <c r="FJ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FK12" t="n">
-        <v>-0.07078256356165689</v>
+        <v>-0.07359132410606854</v>
       </c>
       <c r="FL12" t="n">
         <v>0</v>
       </c>
       <c r="FM12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN12" t="n">
         <v>-0</v>
@@ -7202,19 +7202,19 @@
         <v>0</v>
       </c>
       <c r="FP12" t="n">
-        <v>0.0001972751179710252</v>
+        <v>0.001733354911055457</v>
       </c>
       <c r="FQ12" t="n">
-        <v>-0.08326758169622579</v>
+        <v>0.04137018875311788</v>
       </c>
       <c r="FR12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS12" t="n">
         <v>-0</v>
       </c>
       <c r="FT12" t="n">
-        <v>-0.03655735865324276</v>
+        <v>0.04253352072759832</v>
       </c>
       <c r="FU12" t="n">
         <v>-0</v>
@@ -7229,13 +7229,13 @@
         <v>-0</v>
       </c>
       <c r="FY12" t="n">
-        <v>-0.154137174692875</v>
+        <v>0.003739765235995837</v>
       </c>
       <c r="FZ12" t="n">
-        <v>-0.05163738555133192</v>
+        <v>-0.009501969457267391</v>
       </c>
       <c r="GA12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB12" t="n">
         <v>-0</v>
@@ -7244,7 +7244,7 @@
         <v>0</v>
       </c>
       <c r="GD12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE12" t="n">
         <v>-0</v>
@@ -7253,7 +7253,7 @@
         <v>-0</v>
       </c>
       <c r="GG12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -7261,7 +7261,7 @@
         <v>0</v>
       </c>
       <c r="B13" t="n">
-        <v>0.1496082658998431</v>
+        <v>0.3050360095745513</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
@@ -7270,10 +7270,10 @@
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.05050764279610264</v>
+        <v>0.06400158013401473</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.07783150167930862</v>
+        <v>-0.1674769457784007</v>
       </c>
       <c r="G13" t="n">
         <v>-0</v>
@@ -7285,10 +7285,10 @@
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K13" t="n">
-        <v>0.1084893438066814</v>
+        <v>0.3220272473673892</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -7297,16 +7297,16 @@
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.0206292743286881</v>
+        <v>-0.04571577325023095</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.05058132542063425</v>
+        <v>-0.1470264742236829</v>
       </c>
       <c r="P13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -7315,49 +7315,49 @@
         <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>0.02334656483461089</v>
+        <v>0.1307925820487379</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>-0.01685320739660771</v>
+        <v>-0.03629736835018972</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.0005317449149046421</v>
+        <v>0.001249656014089701</v>
       </c>
       <c r="Y13" t="n">
         <v>-0</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.0008385756378535438</v>
+        <v>-0.01662695934095518</v>
       </c>
       <c r="AD13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.006659123548114939</v>
+        <v>-0.0568962331595159</v>
       </c>
       <c r="AG13" t="n">
-        <v>0.003159968205281028</v>
+        <v>0.02126784312271769</v>
       </c>
       <c r="AH13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI13" t="n">
         <v>-0</v>
@@ -7369,34 +7369,34 @@
         <v>0</v>
       </c>
       <c r="AL13" t="n">
-        <v>0.02344061157875744</v>
+        <v>0.09693679564203371</v>
       </c>
       <c r="AM13" t="n">
         <v>-0</v>
       </c>
       <c r="AN13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO13" t="n">
-        <v>0.002593447887551928</v>
+        <v>-0.03597150667206924</v>
       </c>
       <c r="AP13" t="n">
-        <v>-0.03903432690755655</v>
+        <v>-0.06297048187075689</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR13" t="n">
         <v>-0</v>
       </c>
       <c r="AS13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU13" t="n">
-        <v>0.1136875712437861</v>
+        <v>0.5815704534895814</v>
       </c>
       <c r="AV13" t="n">
         <v>-0</v>
@@ -7405,25 +7405,25 @@
         <v>0</v>
       </c>
       <c r="AX13" t="n">
-        <v>-0.03927614719870123</v>
+        <v>-0.209841477600869</v>
       </c>
       <c r="AY13" t="n">
-        <v>-0.09202787207415655</v>
+        <v>-0.2608453366049366</v>
       </c>
       <c r="AZ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA13" t="n">
         <v>-0</v>
       </c>
       <c r="BB13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC13" t="n">
         <v>0</v>
       </c>
       <c r="BD13" t="n">
-        <v>0.03546575413379773</v>
+        <v>-0.1438077140173589</v>
       </c>
       <c r="BE13" t="n">
         <v>0</v>
@@ -7432,70 +7432,70 @@
         <v>0</v>
       </c>
       <c r="BG13" t="n">
-        <v>-0.0357400211000821</v>
+        <v>0.002736302381433662</v>
       </c>
       <c r="BH13" t="n">
-        <v>-0.02229286350805137</v>
+        <v>-0.06537678521096568</v>
       </c>
       <c r="BI13" t="n">
         <v>-0</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK13" t="n">
         <v>0</v>
       </c>
       <c r="BL13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.02482467292587764</v>
+        <v>0.1330822170123771</v>
       </c>
       <c r="BN13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO13" t="n">
         <v>-0</v>
       </c>
       <c r="BP13" t="n">
-        <v>-0.002546648575107513</v>
+        <v>0.08781500073323319</v>
       </c>
       <c r="BQ13" t="n">
-        <v>0.00642027549446862</v>
+        <v>0.04154053642638391</v>
       </c>
       <c r="BR13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS13" t="n">
         <v>0</v>
       </c>
       <c r="BT13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU13" t="n">
         <v>-0</v>
       </c>
       <c r="BV13" t="n">
-        <v>0.06189139438839626</v>
+        <v>0.3211102710153835</v>
       </c>
       <c r="BW13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX13" t="n">
         <v>0</v>
       </c>
       <c r="BY13" t="n">
-        <v>-0.02653877200269847</v>
+        <v>-0.0408279562914721</v>
       </c>
       <c r="BZ13" t="n">
-        <v>-0.02640025337916411</v>
+        <v>-0.09459072376677409</v>
       </c>
       <c r="CA13" t="n">
         <v>-0</v>
       </c>
       <c r="CB13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC13" t="n">
         <v>-0</v>
@@ -7504,34 +7504,34 @@
         <v>0</v>
       </c>
       <c r="CE13" t="n">
-        <v>-0.0311781498043518</v>
+        <v>-0.1293280273265344</v>
       </c>
       <c r="CF13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG13" t="n">
         <v>-0</v>
       </c>
       <c r="CH13" t="n">
-        <v>0.001258627113071169</v>
+        <v>0.0143163492904592</v>
       </c>
       <c r="CI13" t="n">
-        <v>0.02452932073712738</v>
+        <v>0.05694484722510691</v>
       </c>
       <c r="CJ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK13" t="n">
         <v>0</v>
       </c>
       <c r="CL13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM13" t="n">
         <v>0</v>
       </c>
       <c r="CN13" t="n">
-        <v>0.005738668127066465</v>
+        <v>-0.1248799943468115</v>
       </c>
       <c r="CO13" t="n">
         <v>-0</v>
@@ -7540,37 +7540,37 @@
         <v>-0</v>
       </c>
       <c r="CQ13" t="n">
-        <v>-0.0005489756660519262</v>
+        <v>0.08676040793352575</v>
       </c>
       <c r="CR13" t="n">
-        <v>-0.01799896468366113</v>
+        <v>0.01934352001336341</v>
       </c>
       <c r="CS13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV13" t="n">
         <v>-0</v>
       </c>
       <c r="CW13" t="n">
-        <v>-0.02854765388914949</v>
+        <v>-0.121853981263481</v>
       </c>
       <c r="CX13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY13" t="n">
         <v>0</v>
       </c>
       <c r="CZ13" t="n">
-        <v>0.003458761725712044</v>
+        <v>-0.006596791421021745</v>
       </c>
       <c r="DA13" t="n">
-        <v>0.03034752932369078</v>
+        <v>0.09029453842520681</v>
       </c>
       <c r="DB13" t="n">
         <v>0</v>
@@ -7579,40 +7579,40 @@
         <v>-0</v>
       </c>
       <c r="DD13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF13" t="n">
-        <v>-0.02038873561903875</v>
+        <v>-0.1264886436581259</v>
       </c>
       <c r="DG13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.04198357010656961</v>
+        <v>-0.1615775342278365</v>
       </c>
       <c r="DJ13" t="n">
-        <v>-0.0009766352999453886</v>
+        <v>0.05476920091127242</v>
       </c>
       <c r="DK13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DL13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DM13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO13" t="n">
-        <v>-0.00963550648505076</v>
+        <v>-0.08130355478301605</v>
       </c>
       <c r="DP13" t="n">
         <v>0</v>
@@ -7621,37 +7621,37 @@
         <v>0</v>
       </c>
       <c r="DR13" t="n">
-        <v>0.013568503397487</v>
+        <v>0.01310651678105894</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.000199566948178412</v>
+        <v>0.08248656422432123</v>
       </c>
       <c r="DT13" t="n">
         <v>-0</v>
       </c>
       <c r="DU13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV13" t="n">
         <v>0</v>
       </c>
       <c r="DW13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX13" t="n">
-        <v>-0.02125698854071172</v>
+        <v>-0.1140297928281721</v>
       </c>
       <c r="DY13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ13" t="n">
         <v>-0</v>
       </c>
       <c r="EA13" t="n">
-        <v>0.007038951875142824</v>
+        <v>0.01022053976577308</v>
       </c>
       <c r="EB13" t="n">
-        <v>0.008982954013516599</v>
+        <v>0.03711994863384966</v>
       </c>
       <c r="EC13" t="n">
         <v>0</v>
@@ -7660,25 +7660,25 @@
         <v>0</v>
       </c>
       <c r="EE13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF13" t="n">
         <v>0</v>
       </c>
       <c r="EG13" t="n">
-        <v>-0.03249091348122058</v>
+        <v>-0.03528280158771884</v>
       </c>
       <c r="EH13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI13" t="n">
         <v>-0</v>
       </c>
       <c r="EJ13" t="n">
-        <v>0.01244890074491323</v>
+        <v>-0.0335965439248038</v>
       </c>
       <c r="EK13" t="n">
-        <v>0.03448664767752143</v>
+        <v>-0.03569887343870646</v>
       </c>
       <c r="EL13" t="n">
         <v>-0</v>
@@ -7693,22 +7693,22 @@
         <v>0</v>
       </c>
       <c r="EP13" t="n">
-        <v>-0.01780821487346118</v>
+        <v>-0.01155727800894668</v>
       </c>
       <c r="EQ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER13" t="n">
         <v>-0</v>
       </c>
       <c r="ES13" t="n">
-        <v>-0.0009834098558741153</v>
+        <v>-0.08928045134940379</v>
       </c>
       <c r="ET13" t="n">
-        <v>0.009587972805082567</v>
+        <v>-0.02867918146376466</v>
       </c>
       <c r="EU13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV13" t="n">
         <v>0</v>
@@ -7720,46 +7720,46 @@
         <v>0</v>
       </c>
       <c r="EY13" t="n">
-        <v>-0.02666139601646762</v>
+        <v>-0.1514071899892321</v>
       </c>
       <c r="EZ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA13" t="n">
         <v>-0</v>
       </c>
       <c r="FB13" t="n">
-        <v>0.003533873754926275</v>
+        <v>-0.01409304341797898</v>
       </c>
       <c r="FC13" t="n">
-        <v>0.02634767334706528</v>
+        <v>0.06864013689897967</v>
       </c>
       <c r="FD13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FF13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH13" t="n">
-        <v>-0.001280893963123695</v>
+        <v>0.09563859468352894</v>
       </c>
       <c r="FI13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ13" t="n">
         <v>-0</v>
       </c>
       <c r="FK13" t="n">
-        <v>0.01007008216087361</v>
+        <v>-0.03238144428424074</v>
       </c>
       <c r="FL13" t="n">
-        <v>0.03176563858496266</v>
+        <v>0.1261001429295096</v>
       </c>
       <c r="FM13" t="n">
         <v>0</v>
@@ -7771,10 +7771,10 @@
         <v>0</v>
       </c>
       <c r="FP13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ13" t="n">
-        <v>-0.00281222217637857</v>
+        <v>-0.0277405752607051</v>
       </c>
       <c r="FR13" t="n">
         <v>-0</v>
@@ -7783,43 +7783,43 @@
         <v>-0</v>
       </c>
       <c r="FT13" t="n">
-        <v>0.01125035671199754</v>
+        <v>0.05554611827105121</v>
       </c>
       <c r="FU13" t="n">
-        <v>0.01700353811588047</v>
+        <v>-0.0895617121026107</v>
       </c>
       <c r="FV13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ13" t="n">
-        <v>0.004676091419725967</v>
+        <v>-0.05214476896110549</v>
       </c>
       <c r="GA13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB13" t="n">
         <v>0</v>
       </c>
       <c r="GC13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD13" t="n">
-        <v>-0.01839851382954323</v>
+        <v>0.09411891491589483</v>
       </c>
       <c r="GE13" t="n">
         <v>-0</v>
       </c>
       <c r="GF13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG13" t="n">
         <v>-0</v>
@@ -7830,7 +7830,7 @@
         <v>0</v>
       </c>
       <c r="B14" t="n">
-        <v>0.1020841332879855</v>
+        <v>0.1526417087678394</v>
       </c>
       <c r="C14" t="n">
         <v>0</v>
@@ -7839,40 +7839,40 @@
         <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.08402052929767165</v>
+        <v>-0.04405886601086263</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.0169935866552945</v>
+        <v>-0.05981421938115108</v>
       </c>
       <c r="G14" t="n">
         <v>-0</v>
       </c>
       <c r="H14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K14" t="n">
-        <v>0.06421677013463198</v>
+        <v>0.1637992852416496</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.05771565482580825</v>
+        <v>-0.07902204596326383</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.01306626349716746</v>
+        <v>-0.05600794788109285</v>
       </c>
       <c r="P14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -7881,10 +7881,10 @@
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T14" t="n">
-        <v>0.02156141023026783</v>
+        <v>0.06231846372131986</v>
       </c>
       <c r="U14" t="n">
         <v>0</v>
@@ -7893,37 +7893,37 @@
         <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>-0.008322170071173819</v>
+        <v>-0.05466236353752718</v>
       </c>
       <c r="X14" t="n">
-        <v>0.01045900277248337</v>
+        <v>0.003164034593307104</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>0.003494791878018157</v>
+        <v>-0.02371477780636356</v>
       </c>
       <c r="AD14" t="n">
         <v>-0</v>
       </c>
       <c r="AE14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.003611691802032547</v>
+        <v>-0.06230904846397898</v>
       </c>
       <c r="AG14" t="n">
-        <v>0.003468238058667024</v>
+        <v>0.00555231336475926</v>
       </c>
       <c r="AH14" t="n">
         <v>0</v>
@@ -7935,28 +7935,28 @@
         <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL14" t="n">
-        <v>0.01693600797579485</v>
+        <v>0.01683485723967399</v>
       </c>
       <c r="AM14" t="n">
         <v>-0</v>
       </c>
       <c r="AN14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO14" t="n">
-        <v>-0.01312647997872498</v>
+        <v>-0.0437589812754258</v>
       </c>
       <c r="AP14" t="n">
-        <v>-0.01509425824321281</v>
+        <v>0.004398188360805986</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS14" t="n">
         <v>0</v>
@@ -7965,7 +7965,7 @@
         <v>-0</v>
       </c>
       <c r="AU14" t="n">
-        <v>0.09172262013028937</v>
+        <v>0.2074253403035326</v>
       </c>
       <c r="AV14" t="n">
         <v>-0</v>
@@ -7974,10 +7974,10 @@
         <v>0</v>
       </c>
       <c r="AX14" t="n">
-        <v>-0.04856937190885982</v>
+        <v>-0.1288116338023894</v>
       </c>
       <c r="AY14" t="n">
-        <v>-0.0144052958861114</v>
+        <v>-0.1069601757748156</v>
       </c>
       <c r="AZ14" t="n">
         <v>0</v>
@@ -7986,13 +7986,13 @@
         <v>-0</v>
       </c>
       <c r="BB14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC14" t="n">
         <v>0</v>
       </c>
       <c r="BD14" t="n">
-        <v>0.0195207084017245</v>
+        <v>-0.02065822284424913</v>
       </c>
       <c r="BE14" t="n">
         <v>0</v>
@@ -8001,64 +8001,64 @@
         <v>0</v>
       </c>
       <c r="BG14" t="n">
-        <v>-0.05422323863266254</v>
+        <v>-0.01425059198536224</v>
       </c>
       <c r="BH14" t="n">
-        <v>-0.01060783340913262</v>
+        <v>-0.01378818716350386</v>
       </c>
       <c r="BI14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK14" t="n">
         <v>0</v>
       </c>
       <c r="BL14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.02513539238880621</v>
+        <v>0.02942306444989923</v>
       </c>
       <c r="BN14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BP14" t="n">
-        <v>0.01462339514021655</v>
+        <v>0.06188401198311964</v>
       </c>
       <c r="BQ14" t="n">
-        <v>0.0153860614232823</v>
+        <v>0.02238019032467169</v>
       </c>
       <c r="BR14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS14" t="n">
         <v>-0</v>
       </c>
       <c r="BT14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU14" t="n">
         <v>-0</v>
       </c>
       <c r="BV14" t="n">
-        <v>0.04914350702308985</v>
+        <v>0.1248429803318388</v>
       </c>
       <c r="BW14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX14" t="n">
         <v>0</v>
       </c>
       <c r="BY14" t="n">
-        <v>-0.02666337425894548</v>
+        <v>-0.03915003073539105</v>
       </c>
       <c r="BZ14" t="n">
-        <v>0.002590875586360009</v>
+        <v>-0.03214712190446828</v>
       </c>
       <c r="CA14" t="n">
         <v>-0</v>
@@ -8067,40 +8067,40 @@
         <v>-0</v>
       </c>
       <c r="CC14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE14" t="n">
-        <v>-0.01814226709795432</v>
+        <v>-0.0419082847597705</v>
       </c>
       <c r="CF14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG14" t="n">
         <v>-0</v>
       </c>
       <c r="CH14" t="n">
-        <v>0.01381361616338777</v>
+        <v>0.02690499250766374</v>
       </c>
       <c r="CI14" t="n">
-        <v>0.006292756465611227</v>
+        <v>0.03597608880649066</v>
       </c>
       <c r="CJ14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK14" t="n">
         <v>-0</v>
       </c>
       <c r="CL14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CM14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CN14" t="n">
-        <v>0.0003910181451737072</v>
+        <v>-0.03340721576637444</v>
       </c>
       <c r="CO14" t="n">
         <v>-0</v>
@@ -8109,37 +8109,37 @@
         <v>-0</v>
       </c>
       <c r="CQ14" t="n">
-        <v>-0.002831175779817538</v>
+        <v>0.05324666581245086</v>
       </c>
       <c r="CR14" t="n">
-        <v>-0.007262926825804069</v>
+        <v>0.02047171867909928</v>
       </c>
       <c r="CS14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT14" t="n">
         <v>0</v>
       </c>
       <c r="CU14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW14" t="n">
-        <v>-0.01279802266547996</v>
+        <v>-0.04324501792446724</v>
       </c>
       <c r="CX14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY14" t="n">
         <v>0</v>
       </c>
       <c r="CZ14" t="n">
-        <v>0.0122677994742888</v>
+        <v>0.02197854092911719</v>
       </c>
       <c r="DA14" t="n">
-        <v>0.01174170143216478</v>
+        <v>0.05166613967004771</v>
       </c>
       <c r="DB14" t="n">
         <v>-0</v>
@@ -8148,25 +8148,25 @@
         <v>0</v>
       </c>
       <c r="DD14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DE14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DF14" t="n">
-        <v>-0.01421292064359185</v>
+        <v>-0.04329792637302853</v>
       </c>
       <c r="DG14" t="n">
         <v>-0</v>
       </c>
       <c r="DH14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI14" t="n">
-        <v>0.0181035049481498</v>
+        <v>-0.04405949083624984</v>
       </c>
       <c r="DJ14" t="n">
-        <v>-0.00294719262654576</v>
+        <v>0.0152685473126377</v>
       </c>
       <c r="DK14" t="n">
         <v>0</v>
@@ -8175,106 +8175,106 @@
         <v>-0</v>
       </c>
       <c r="DM14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN14" t="n">
         <v>-0</v>
       </c>
       <c r="DO14" t="n">
-        <v>-0.004275381857019834</v>
+        <v>0.007095946239171823</v>
       </c>
       <c r="DP14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ14" t="n">
         <v>0</v>
       </c>
       <c r="DR14" t="n">
-        <v>0.02153534443819882</v>
+        <v>-0.02386975835392742</v>
       </c>
       <c r="DS14" t="n">
-        <v>-0.009109462437326936</v>
+        <v>-0.01317855735874414</v>
       </c>
       <c r="DT14" t="n">
         <v>-0</v>
       </c>
       <c r="DU14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW14" t="n">
         <v>0</v>
       </c>
       <c r="DX14" t="n">
-        <v>-0.01956926762507731</v>
+        <v>-0.008242463904672601</v>
       </c>
       <c r="DY14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DZ14" t="n">
         <v>-0</v>
       </c>
       <c r="EA14" t="n">
-        <v>0.01936645685144719</v>
+        <v>-0.003409090674396716</v>
       </c>
       <c r="EB14" t="n">
-        <v>-0.004632107804889072</v>
+        <v>0.02712466787466808</v>
       </c>
       <c r="EC14" t="n">
         <v>-0</v>
       </c>
       <c r="ED14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EE14" t="n">
         <v>-0</v>
       </c>
       <c r="EF14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG14" t="n">
-        <v>-0.02045058312696749</v>
+        <v>-0.02382702979715013</v>
       </c>
       <c r="EH14" t="n">
         <v>-0</v>
       </c>
       <c r="EI14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ14" t="n">
-        <v>0.01249634226870981</v>
+        <v>0.01579363437080824</v>
       </c>
       <c r="EK14" t="n">
-        <v>0.009048908578283589</v>
+        <v>0.01015815764016457</v>
       </c>
       <c r="EL14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM14" t="n">
         <v>-0</v>
       </c>
       <c r="EN14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO14" t="n">
         <v>0</v>
       </c>
       <c r="EP14" t="n">
-        <v>-0.002809502266768191</v>
+        <v>-0.02416843350541758</v>
       </c>
       <c r="EQ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER14" t="n">
         <v>-0</v>
       </c>
       <c r="ES14" t="n">
-        <v>0.006389502698110698</v>
+        <v>0.01950102461616521</v>
       </c>
       <c r="ET14" t="n">
-        <v>-0.004764912773717733</v>
+        <v>0.05259189920909937</v>
       </c>
       <c r="EU14" t="n">
         <v>0</v>
@@ -8283,25 +8283,25 @@
         <v>0</v>
       </c>
       <c r="EW14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY14" t="n">
-        <v>-0.01221428599050072</v>
+        <v>-0.04862495502780667</v>
       </c>
       <c r="EZ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA14" t="n">
         <v>-0</v>
       </c>
       <c r="FB14" t="n">
-        <v>0.01293285921557576</v>
+        <v>0.01479844806877751</v>
       </c>
       <c r="FC14" t="n">
-        <v>0.01223946426423255</v>
+        <v>0.03404565480886572</v>
       </c>
       <c r="FD14" t="n">
         <v>0</v>
@@ -8313,10 +8313,10 @@
         <v>-0</v>
       </c>
       <c r="FG14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH14" t="n">
-        <v>-0.00403781842391285</v>
+        <v>0.05805849620830821</v>
       </c>
       <c r="FI14" t="n">
         <v>-0</v>
@@ -8325,16 +8325,16 @@
         <v>-0</v>
       </c>
       <c r="FK14" t="n">
-        <v>0.01522466675568582</v>
+        <v>-0.02526074963024479</v>
       </c>
       <c r="FL14" t="n">
-        <v>0.01344791572013587</v>
+        <v>0.02753451299386094</v>
       </c>
       <c r="FM14" t="n">
         <v>0</v>
       </c>
       <c r="FN14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO14" t="n">
         <v>0</v>
@@ -8343,7 +8343,7 @@
         <v>0</v>
       </c>
       <c r="FQ14" t="n">
-        <v>-0.002808898544490414</v>
+        <v>-0.01184390393513543</v>
       </c>
       <c r="FR14" t="n">
         <v>-0</v>
@@ -8352,40 +8352,40 @@
         <v>-0</v>
       </c>
       <c r="FT14" t="n">
-        <v>0.00750255434764861</v>
+        <v>0.02013282042754272</v>
       </c>
       <c r="FU14" t="n">
-        <v>0.008923002870434887</v>
+        <v>-0.05632865238998719</v>
       </c>
       <c r="FV14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ14" t="n">
-        <v>-0.005217629771249037</v>
+        <v>-0.03858203107362491</v>
       </c>
       <c r="GA14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB14" t="n">
         <v>-0</v>
       </c>
       <c r="GC14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD14" t="n">
-        <v>-0.008427603097652331</v>
+        <v>0.05626918471806199</v>
       </c>
       <c r="GE14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF14" t="n">
         <v>-0</v>
@@ -8396,49 +8396,49 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="B15" t="n">
-        <v>0.3908482284799203</v>
+        <v>0.27906341140928</v>
       </c>
       <c r="C15" t="n">
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.1415305532121398</v>
+        <v>-0.1721047405623718</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.03734246700600252</v>
+        <v>-0.05382423867111009</v>
       </c>
       <c r="F15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I15" t="n">
         <v>-0</v>
       </c>
       <c r="J15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0.2684824886632711</v>
+        <v>0.2817095067108163</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.1467026088088991</v>
+        <v>-0.2178468124267593</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.05606121135248502</v>
+        <v>-0.09647993297298611</v>
       </c>
       <c r="O15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
         <v>-0</v>
@@ -8447,139 +8447,139 @@
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>0.1025781878612301</v>
+        <v>0.05092960879709795</v>
       </c>
       <c r="U15" t="n">
         <v>-0</v>
       </c>
       <c r="V15" t="n">
-        <v>0.005887372055981032</v>
+        <v>-0.03742790870700537</v>
       </c>
       <c r="W15" t="n">
-        <v>0.1023360302370037</v>
+        <v>-0.0171264904303167</v>
       </c>
       <c r="X15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
         <v>-0</v>
       </c>
       <c r="AA15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>0.1019684851844056</v>
+        <v>-0.004663533305219917</v>
       </c>
       <c r="AD15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>-0.01040495651815334</v>
+        <v>-0.03984156522691736</v>
       </c>
       <c r="AF15" t="n">
-        <v>-0.003349430925435355</v>
+        <v>-0.02678072304639451</v>
       </c>
       <c r="AG15" t="n">
         <v>-0</v>
       </c>
       <c r="AH15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK15" t="n">
         <v>0</v>
       </c>
       <c r="AL15" t="n">
-        <v>-0.01435144831739498</v>
+        <v>0.05565911060018083</v>
       </c>
       <c r="AM15" t="n">
         <v>-0</v>
       </c>
       <c r="AN15" t="n">
-        <v>-0.07636656378673791</v>
+        <v>-0.03304216043460818</v>
       </c>
       <c r="AO15" t="n">
-        <v>-0.08922455505332197</v>
+        <v>0.0367403440813706</v>
       </c>
       <c r="AP15" t="n">
         <v>0</v>
       </c>
       <c r="AQ15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR15" t="n">
         <v>-0</v>
       </c>
       <c r="AS15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AT15" t="n">
         <v>-0</v>
       </c>
       <c r="AU15" t="n">
-        <v>0.3359384194582907</v>
+        <v>0.221396695599989</v>
       </c>
       <c r="AV15" t="n">
         <v>-0</v>
       </c>
       <c r="AW15" t="n">
-        <v>-0.07319756489617422</v>
+        <v>-0.1554939418839317</v>
       </c>
       <c r="AX15" t="n">
-        <v>0.1419134082802872</v>
+        <v>-0.1579171260080268</v>
       </c>
       <c r="AY15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ15" t="n">
         <v>-0</v>
       </c>
       <c r="BA15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB15" t="n">
         <v>-0</v>
       </c>
       <c r="BC15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD15" t="n">
-        <v>0.02797713467093448</v>
+        <v>0.002010825938985683</v>
       </c>
       <c r="BE15" t="n">
         <v>0</v>
       </c>
       <c r="BF15" t="n">
-        <v>-0.05805134466920195</v>
+        <v>-0.05721859337844349</v>
       </c>
       <c r="BG15" t="n">
-        <v>-0.1169422629402479</v>
+        <v>-0.003745060216452424</v>
       </c>
       <c r="BH15" t="n">
         <v>0</v>
       </c>
       <c r="BI15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK15" t="n">
         <v>0</v>
@@ -8588,19 +8588,19 @@
         <v>-0</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.05694798247597166</v>
+        <v>0.001550845906381617</v>
       </c>
       <c r="BN15" t="n">
         <v>-0</v>
       </c>
       <c r="BO15" t="n">
-        <v>0.05899851120585817</v>
+        <v>0.07723452355695716</v>
       </c>
       <c r="BP15" t="n">
-        <v>0.1979007751952771</v>
+        <v>0.04788186151710333</v>
       </c>
       <c r="BQ15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR15" t="n">
         <v>0</v>
@@ -8609,22 +8609,22 @@
         <v>-0</v>
       </c>
       <c r="BT15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU15" t="n">
         <v>-0</v>
       </c>
       <c r="BV15" t="n">
-        <v>0.1604826507973125</v>
+        <v>0.1761781259607639</v>
       </c>
       <c r="BW15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX15" t="n">
-        <v>0.01855643253586027</v>
+        <v>-0.111658041366504</v>
       </c>
       <c r="BY15" t="n">
-        <v>0.09865811961175174</v>
+        <v>-0.02389575488586959</v>
       </c>
       <c r="BZ15" t="n">
         <v>0</v>
@@ -8633,106 +8633,106 @@
         <v>-0</v>
       </c>
       <c r="CB15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD15" t="n">
         <v>0</v>
       </c>
       <c r="CE15" t="n">
-        <v>-0.08985607678154689</v>
+        <v>-0.07788387425564711</v>
       </c>
       <c r="CF15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG15" t="n">
-        <v>0.02646568059917847</v>
+        <v>0.09937519027483141</v>
       </c>
       <c r="CH15" t="n">
-        <v>-0.01216717102087097</v>
+        <v>0.01030230388279605</v>
       </c>
       <c r="CI15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK15" t="n">
         <v>0</v>
       </c>
       <c r="CL15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CM15" t="n">
         <v>0</v>
       </c>
       <c r="CN15" t="n">
-        <v>-0.02373886836111925</v>
+        <v>-0.05365453480748476</v>
       </c>
       <c r="CO15" t="n">
         <v>-0</v>
       </c>
       <c r="CP15" t="n">
-        <v>-0.06123675580626253</v>
+        <v>0.1145605739243254</v>
       </c>
       <c r="CQ15" t="n">
-        <v>-0.1073901702012416</v>
+        <v>0.04883081840980789</v>
       </c>
       <c r="CR15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CU15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV15" t="n">
         <v>-0</v>
       </c>
       <c r="CW15" t="n">
-        <v>-0.08553426522495343</v>
+        <v>-0.08834934784503301</v>
       </c>
       <c r="CX15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY15" t="n">
-        <v>0.04541795342960152</v>
+        <v>0.1145525159808156</v>
       </c>
       <c r="CZ15" t="n">
-        <v>-0.004737652662853742</v>
+        <v>0.01894685971002438</v>
       </c>
       <c r="DA15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DB15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC15" t="n">
         <v>-0</v>
       </c>
       <c r="DD15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DE15" t="n">
         <v>0</v>
       </c>
       <c r="DF15" t="n">
-        <v>-0.01167532022366577</v>
+        <v>-0.03018910362918232</v>
       </c>
       <c r="DG15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH15" t="n">
-        <v>0.00522976608010529</v>
+        <v>0.02255883947343936</v>
       </c>
       <c r="DI15" t="n">
-        <v>-0.008584961919464862</v>
+        <v>-0.04433147355759415</v>
       </c>
       <c r="DJ15" t="n">
         <v>-0</v>
@@ -8747,19 +8747,19 @@
         <v>0</v>
       </c>
       <c r="DN15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO15" t="n">
-        <v>-0.006211831031062068</v>
+        <v>-0.03911175051430004</v>
       </c>
       <c r="DP15" t="n">
         <v>0</v>
       </c>
       <c r="DQ15" t="n">
-        <v>-0.1762713406829348</v>
+        <v>0.02841086132839993</v>
       </c>
       <c r="DR15" t="n">
-        <v>-0.04817659476881336</v>
+        <v>0.005100622281625763</v>
       </c>
       <c r="DS15" t="n">
         <v>-0</v>
@@ -8768,85 +8768,85 @@
         <v>-0</v>
       </c>
       <c r="DU15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX15" t="n">
-        <v>-0.06411067244608598</v>
+        <v>-0.02634008135294045</v>
       </c>
       <c r="DY15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ15" t="n">
-        <v>0.009830828483425074</v>
+        <v>0.03298517806692933</v>
       </c>
       <c r="EA15" t="n">
-        <v>0.03959695257008852</v>
+        <v>-0.04846634956167581</v>
       </c>
       <c r="EB15" t="n">
         <v>0</v>
       </c>
       <c r="EC15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF15" t="n">
         <v>0</v>
       </c>
       <c r="EG15" t="n">
-        <v>-0.1085980045543459</v>
+        <v>-0.0634134743568055</v>
       </c>
       <c r="EH15" t="n">
         <v>0</v>
       </c>
       <c r="EI15" t="n">
-        <v>0.08250780357661347</v>
+        <v>0.08967125266665757</v>
       </c>
       <c r="EJ15" t="n">
-        <v>0.07410638221299015</v>
+        <v>0.02648468372586095</v>
       </c>
       <c r="EK15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL15" t="n">
         <v>-0</v>
       </c>
       <c r="EM15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO15" t="n">
         <v>0</v>
       </c>
       <c r="EP15" t="n">
-        <v>-0.09174763403608648</v>
+        <v>-0.03152943386805694</v>
       </c>
       <c r="EQ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER15" t="n">
-        <v>0.08213835254051061</v>
+        <v>0.06389111200061728</v>
       </c>
       <c r="ES15" t="n">
-        <v>0.01346117157503463</v>
+        <v>-0.0114215228907196</v>
       </c>
       <c r="ET15" t="n">
         <v>0</v>
       </c>
       <c r="EU15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV15" t="n">
         <v>0</v>
@@ -8858,43 +8858,43 @@
         <v>0</v>
       </c>
       <c r="EY15" t="n">
-        <v>-0.08093175669359416</v>
+        <v>-0.101879262727118</v>
       </c>
       <c r="EZ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA15" t="n">
-        <v>0.0301811700528325</v>
+        <v>0.118328371998942</v>
       </c>
       <c r="FB15" t="n">
-        <v>-0.002043848056553023</v>
+        <v>0.01088325071226271</v>
       </c>
       <c r="FC15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FD15" t="n">
         <v>0</v>
       </c>
       <c r="FE15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF15" t="n">
         <v>-0</v>
       </c>
       <c r="FG15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH15" t="n">
-        <v>-0.03017341466913788</v>
+        <v>0.06845673470906528</v>
       </c>
       <c r="FI15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ15" t="n">
-        <v>-0.08295084516729991</v>
+        <v>-0.1027733631118575</v>
       </c>
       <c r="FK15" t="n">
-        <v>0.03856790091758881</v>
+        <v>-0.004776499118770632</v>
       </c>
       <c r="FL15" t="n">
         <v>-0</v>
@@ -8906,22 +8906,22 @@
         <v>0</v>
       </c>
       <c r="FO15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ15" t="n">
-        <v>-0.01315159667940698</v>
+        <v>-0.02651647477654762</v>
       </c>
       <c r="FR15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS15" t="n">
-        <v>0.1149543109851126</v>
+        <v>0.09113220629235091</v>
       </c>
       <c r="FT15" t="n">
-        <v>-0.005635113998638619</v>
+        <v>0.05896616290262913</v>
       </c>
       <c r="FU15" t="n">
         <v>-0</v>
@@ -8939,25 +8939,25 @@
         <v>-0</v>
       </c>
       <c r="FZ15" t="n">
-        <v>0.0118155659803467</v>
+        <v>-0.03810200020311424</v>
       </c>
       <c r="GA15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB15" t="n">
-        <v>-0.06156492650544612</v>
+        <v>0.05435217845283753</v>
       </c>
       <c r="GC15" t="n">
         <v>-0</v>
       </c>
       <c r="GD15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG15" t="n">
         <v>-0</v>
@@ -9537,7 +9537,7 @@
         <v>0</v>
       </c>
       <c r="B17" t="n">
-        <v>0.2146974991055687</v>
+        <v>0.4373872719203684</v>
       </c>
       <c r="C17" t="n">
         <v>0</v>
@@ -9546,13 +9546,13 @@
         <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.06166249570091765</v>
+        <v>0.1166710417576716</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.1372065465011049</v>
+        <v>-0.2320435110246692</v>
       </c>
       <c r="G17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
         <v>-0</v>
@@ -9564,25 +9564,25 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0.1651538173850599</v>
+        <v>0.5463597474224761</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.03101471768801332</v>
+        <v>0.03738929178112004</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.1097344187097961</v>
+        <v>-0.1683664257590028</v>
       </c>
       <c r="P17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -9591,7 +9591,7 @@
         <v>-0</v>
       </c>
       <c r="T17" t="n">
-        <v>0.02379762877177963</v>
+        <v>0.1384588586210726</v>
       </c>
       <c r="U17" t="n">
         <v>0</v>
@@ -9600,16 +9600,16 @@
         <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>-0.01635128109844269</v>
+        <v>-0.1191741736161786</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.004275735685908793</v>
+        <v>-0.03541747817658387</v>
       </c>
       <c r="Y17" t="n">
         <v>-0</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA17" t="n">
         <v>0</v>
@@ -9618,22 +9618,22 @@
         <v>-0</v>
       </c>
       <c r="AC17" t="n">
-        <v>0.006215450076922325</v>
+        <v>0.007887111454452754</v>
       </c>
       <c r="AD17" t="n">
         <v>-0</v>
       </c>
       <c r="AE17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.01330545012385246</v>
+        <v>-0.2957807775175201</v>
       </c>
       <c r="AG17" t="n">
-        <v>-7.992590638328244e-05</v>
+        <v>-0.0907955681389889</v>
       </c>
       <c r="AH17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI17" t="n">
         <v>-0</v>
@@ -9645,7 +9645,7 @@
         <v>0</v>
       </c>
       <c r="AL17" t="n">
-        <v>0.03052688726185477</v>
+        <v>0.1301198132250574</v>
       </c>
       <c r="AM17" t="n">
         <v>0</v>
@@ -9654,10 +9654,10 @@
         <v>0</v>
       </c>
       <c r="AO17" t="n">
-        <v>0.00331143344402303</v>
+        <v>-0.02788449165221842</v>
       </c>
       <c r="AP17" t="n">
-        <v>-0.03842386836336169</v>
+        <v>-0.09144642039184242</v>
       </c>
       <c r="AQ17" t="n">
         <v>-0</v>
@@ -9669,10 +9669,10 @@
         <v>0</v>
       </c>
       <c r="AT17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU17" t="n">
-        <v>0.1481128656561646</v>
+        <v>0.6675610584297661</v>
       </c>
       <c r="AV17" t="n">
         <v>-0</v>
@@ -9681,25 +9681,25 @@
         <v>0</v>
       </c>
       <c r="AX17" t="n">
-        <v>-0.02382546226205735</v>
+        <v>-0.07582594835978024</v>
       </c>
       <c r="AY17" t="n">
-        <v>-0.07844487785598281</v>
+        <v>-0.1034894064737233</v>
       </c>
       <c r="AZ17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB17" t="n">
         <v>0</v>
       </c>
       <c r="BC17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD17" t="n">
-        <v>0.04047987357956814</v>
+        <v>-0.09997509534723616</v>
       </c>
       <c r="BE17" t="n">
         <v>0</v>
@@ -9708,64 +9708,64 @@
         <v>0</v>
       </c>
       <c r="BG17" t="n">
-        <v>-0.0547000783482053</v>
+        <v>-0.07709411701546948</v>
       </c>
       <c r="BH17" t="n">
-        <v>-0.0534923858599631</v>
+        <v>-0.133600117950018</v>
       </c>
       <c r="BI17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.03926529050770443</v>
+        <v>0.129185666080984</v>
       </c>
       <c r="BN17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO17" t="n">
         <v>-0</v>
       </c>
       <c r="BP17" t="n">
-        <v>0.0005786439610635845</v>
+        <v>0.08863890593199711</v>
       </c>
       <c r="BQ17" t="n">
-        <v>0.0195468211318834</v>
+        <v>-0.02304378903845352</v>
       </c>
       <c r="BR17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU17" t="n">
         <v>0</v>
       </c>
       <c r="BV17" t="n">
-        <v>0.07153860270920621</v>
+        <v>0.3680117004449046</v>
       </c>
       <c r="BW17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX17" t="n">
         <v>0</v>
       </c>
       <c r="BY17" t="n">
-        <v>-0.02562032553457219</v>
+        <v>-0.03779317210690522</v>
       </c>
       <c r="BZ17" t="n">
-        <v>-0.0493928857213525</v>
+        <v>-0.1600603324317908</v>
       </c>
       <c r="CA17" t="n">
         <v>-0</v>
@@ -9780,154 +9780,154 @@
         <v>-0</v>
       </c>
       <c r="CE17" t="n">
-        <v>-0.03638933104603533</v>
+        <v>-0.1535878669499456</v>
       </c>
       <c r="CF17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG17" t="n">
         <v>-0</v>
       </c>
       <c r="CH17" t="n">
-        <v>-0.003425098364924364</v>
+        <v>0.02009266893724536</v>
       </c>
       <c r="CI17" t="n">
-        <v>0.03078446949301888</v>
+        <v>0.09292093522574893</v>
       </c>
       <c r="CJ17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK17" t="n">
         <v>0</v>
       </c>
       <c r="CL17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM17" t="n">
         <v>0</v>
       </c>
       <c r="CN17" t="n">
-        <v>0.006472712784301688</v>
+        <v>-0.2689707929397192</v>
       </c>
       <c r="CO17" t="n">
         <v>-0</v>
       </c>
       <c r="CP17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ17" t="n">
-        <v>-0.005258313761749181</v>
+        <v>0.1314915037980961</v>
       </c>
       <c r="CR17" t="n">
-        <v>-0.01446408998899489</v>
+        <v>0.09621625686236646</v>
       </c>
       <c r="CS17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW17" t="n">
-        <v>-0.027784736787574</v>
+        <v>-0.1432577612998865</v>
       </c>
       <c r="CX17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY17" t="n">
         <v>0</v>
       </c>
       <c r="CZ17" t="n">
-        <v>-0.005347740411477608</v>
+        <v>-0.01873411204436209</v>
       </c>
       <c r="DA17" t="n">
-        <v>0.03427269020423423</v>
+        <v>0.1186474781200755</v>
       </c>
       <c r="DB17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC17" t="n">
         <v>-0</v>
       </c>
       <c r="DD17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE17" t="n">
         <v>0</v>
       </c>
       <c r="DF17" t="n">
-        <v>-0.01034246398226128</v>
+        <v>-0.05145855742107339</v>
       </c>
       <c r="DG17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI17" t="n">
-        <v>0.02967893283345814</v>
+        <v>-0.2355266129709956</v>
       </c>
       <c r="DJ17" t="n">
-        <v>0.001847564716961329</v>
+        <v>0.05962143512777236</v>
       </c>
       <c r="DK17" t="n">
         <v>0</v>
       </c>
       <c r="DL17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DM17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO17" t="n">
-        <v>-0.005260052249227066</v>
+        <v>-0.05974444202084379</v>
       </c>
       <c r="DP17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ17" t="n">
         <v>0</v>
       </c>
       <c r="DR17" t="n">
-        <v>0.02408550440186001</v>
+        <v>0.001688498373567673</v>
       </c>
       <c r="DS17" t="n">
-        <v>-0.0002697735698777041</v>
+        <v>-0.01879478202999783</v>
       </c>
       <c r="DT17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DU17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW17" t="n">
         <v>-0</v>
       </c>
       <c r="DX17" t="n">
-        <v>-0.0204188512343726</v>
+        <v>-0.06575291088250412</v>
       </c>
       <c r="DY17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ17" t="n">
         <v>-0</v>
       </c>
       <c r="EA17" t="n">
-        <v>-0.008115893331866209</v>
+        <v>-0.1893356872725337</v>
       </c>
       <c r="EB17" t="n">
-        <v>0.02432746877151867</v>
+        <v>0.08807557440103797</v>
       </c>
       <c r="EC17" t="n">
         <v>-0</v>
@@ -9939,37 +9939,37 @@
         <v>-0</v>
       </c>
       <c r="EF17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG17" t="n">
-        <v>-0.03967894479605003</v>
+        <v>0.007377219792398275</v>
       </c>
       <c r="EH17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI17" t="n">
         <v>0</v>
       </c>
       <c r="EJ17" t="n">
-        <v>0.01010139768537819</v>
+        <v>-0.08259169066525363</v>
       </c>
       <c r="EK17" t="n">
-        <v>0.03197284549126673</v>
+        <v>0.005439913652093229</v>
       </c>
       <c r="EL17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM17" t="n">
         <v>-0</v>
       </c>
       <c r="EN17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP17" t="n">
-        <v>-0.01394165763703744</v>
+        <v>-0.0457546644988298</v>
       </c>
       <c r="EQ17" t="n">
         <v>0</v>
@@ -9978,79 +9978,79 @@
         <v>-0</v>
       </c>
       <c r="ES17" t="n">
-        <v>-0.01371775719449716</v>
+        <v>-0.04782281586294252</v>
       </c>
       <c r="ET17" t="n">
-        <v>0.01457573055335869</v>
+        <v>0.08862605194867484</v>
       </c>
       <c r="EU17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY17" t="n">
-        <v>-0.02647403098958084</v>
+        <v>-0.169186112108647</v>
       </c>
       <c r="EZ17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA17" t="n">
         <v>-0</v>
       </c>
       <c r="FB17" t="n">
-        <v>-0.004349198245360052</v>
+        <v>-0.05256741744794888</v>
       </c>
       <c r="FC17" t="n">
-        <v>0.03124462316982133</v>
+        <v>0.1053090801395038</v>
       </c>
       <c r="FD17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE17" t="n">
         <v>0</v>
       </c>
       <c r="FF17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH17" t="n">
-        <v>0.0008561665074462474</v>
+        <v>0.185564864074029</v>
       </c>
       <c r="FI17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ17" t="n">
         <v>-0</v>
       </c>
       <c r="FK17" t="n">
-        <v>0.003133390353812409</v>
+        <v>-0.1469938755066164</v>
       </c>
       <c r="FL17" t="n">
-        <v>-0.02123038162692813</v>
+        <v>-0.1839214040883827</v>
       </c>
       <c r="FM17" t="n">
         <v>0</v>
       </c>
       <c r="FN17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO17" t="n">
         <v>0</v>
       </c>
       <c r="FP17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ17" t="n">
-        <v>-0.006582759523880407</v>
+        <v>-0.1150309422622585</v>
       </c>
       <c r="FR17" t="n">
         <v>-0</v>
@@ -10059,46 +10059,46 @@
         <v>-0</v>
       </c>
       <c r="FT17" t="n">
-        <v>0.003925724811692122</v>
+        <v>0.04536955963132481</v>
       </c>
       <c r="FU17" t="n">
-        <v>0.04553411504432513</v>
+        <v>-0.1387912373771158</v>
       </c>
       <c r="FV17" t="n">
         <v>-0</v>
       </c>
       <c r="FW17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ17" t="n">
-        <v>0.02114471914552674</v>
+        <v>0.02789721559144994</v>
       </c>
       <c r="GA17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB17" t="n">
         <v>-0</v>
       </c>
       <c r="GC17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD17" t="n">
-        <v>-0.01705513389702289</v>
+        <v>0.04492026981423372</v>
       </c>
       <c r="GE17" t="n">
         <v>-0</v>
       </c>
       <c r="GF17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
